--- a/FMBrandFY2026FebRollingCost20260420.xlsx
+++ b/FMBrandFY2026FebRollingCost20260420.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VBACostCenterSplit\costcentersplit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBFC97B4-AAC9-48BD-8D4A-8DC7A4FBA192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{507D1D23-E7AD-4557-A668-C5598B424A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{99B376D5-D95C-4C6A-9EA6-86FA5AE6C84D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{F1622DF8-CD92-4CC1-8765-3E84EA19BB17}"/>
   </bookViews>
   <sheets>
     <sheet name="CostCenterGroupBySumResult" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="179">
   <si>
     <t>KL</t>
   </si>
@@ -524,22 +524,13 @@
     <t>Contingency</t>
   </si>
   <si>
-    <t>郑州</t>
-  </si>
-  <si>
-    <t>郑州大卫城</t>
-  </si>
-  <si>
-    <t>KLFMFY2026000001</t>
+    <t>FY2026 新店3</t>
+  </si>
+  <si>
+    <t>KLFMFY2026000003</t>
   </si>
   <si>
     <t>FY26 New Door</t>
-  </si>
-  <si>
-    <t>FY2026 新店3</t>
-  </si>
-  <si>
-    <t>KLFMFY2026000003</t>
   </si>
   <si>
     <t>合计：</t>
@@ -565,6 +556,19 @@
   </si>
   <si>
     <t>KL合计：</t>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>郑州</t>
+  </si>
+  <si>
+    <t>郑州大卫城</t>
+  </si>
+  <si>
+    <t>KLFMFY2026000001</t>
   </si>
   <si>
     <t>杭州In77FM</t>
@@ -1030,8 +1034,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D67E08A-6878-4078-99AE-79933E50492D}">
-  <sheetPr codeName="Sheet5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F05DA3B-EA0E-42DC-A440-422B5AF36738}">
   <dimension ref="A1:DC32"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -6695,32 +6698,32 @@
         <v>107</v>
       </c>
       <c r="E19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="11" t="s">
         <v>161</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>162</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="I19" s="11">
-        <v>5841813202</v>
+        <v>162</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>162</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>110</v>
       </c>
       <c r="K19" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="M19" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="L19" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>164</v>
-      </c>
       <c r="N19" s="11" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="O19" s="12" t="s">
         <v>114</v>
@@ -6777,13 +6780,13 @@
         <v>0</v>
       </c>
       <c r="AI19" s="8">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AJ19" s="8">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL19" s="14">
         <v>0</v>
@@ -6798,13 +6801,13 @@
         <v>0</v>
       </c>
       <c r="AP19" s="8">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AQ19" s="8">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AR19" s="14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS19" s="14">
         <v>0</v>
@@ -6819,13 +6822,13 @@
         <v>0</v>
       </c>
       <c r="AW19" s="8">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AX19" s="8">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AY19" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AZ19" s="14">
         <v>0</v>
@@ -6840,13 +6843,13 @@
         <v>0</v>
       </c>
       <c r="BD19" s="8">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="BE19" s="8">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="BF19" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BG19" s="14">
         <v>0</v>
@@ -6861,13 +6864,13 @@
         <v>0</v>
       </c>
       <c r="BK19" s="8">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="BL19" s="8">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="BM19" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BN19" s="14">
         <v>0</v>
@@ -6876,13 +6879,13 @@
         <v>0</v>
       </c>
       <c r="BP19" s="8">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="BQ19" s="8">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="BR19" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BS19" s="14">
         <v>0</v>
@@ -6954,13 +6957,13 @@
         <v>0</v>
       </c>
       <c r="CP19" s="9">
-        <v>37000</v>
+        <v>16000</v>
       </c>
       <c r="CQ19" s="9">
-        <v>37000</v>
+        <v>16000</v>
       </c>
       <c r="CR19" s="14">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="CS19" s="14">
         <v>0</v>
@@ -6972,10 +6975,10 @@
         <v>0</v>
       </c>
       <c r="CV19" s="8">
-        <v>-37000</v>
+        <v>-16000</v>
       </c>
       <c r="CW19" s="8">
-        <v>-37000</v>
+        <v>-16000</v>
       </c>
       <c r="CX19" s="14">
         <v>0</v>
@@ -6990,10 +6993,10 @@
         <v>0</v>
       </c>
       <c r="DB19" s="8">
-        <v>37000</v>
+        <v>16000</v>
       </c>
       <c r="DC19" s="8">
-        <v>37000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="20" spans="1:107" x14ac:dyDescent="0.3">
@@ -7009,26 +7012,26 @@
         <v>125</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>110</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N20" s="5" t="s">
         <v>129</v>
@@ -7310,321 +7313,386 @@
     <row r="21" spans="1:107" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
-      <c r="C21" s="11" t="s">
-        <v>1</v>
-      </c>
+      <c r="C21" s="11"/>
       <c r="D21" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>165</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
       <c r="G21" s="11"/>
-      <c r="H21" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="N21" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="O21" s="12" t="s">
-        <v>114</v>
-      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="12"/>
       <c r="P21" s="12"/>
       <c r="Q21" s="13"/>
       <c r="R21" s="13"/>
       <c r="S21" s="14">
+        <f>SUM($S$2,$S$3,$S$4,$S$5,$S$6,$S$7,$S$8,$S$9,$S$10,$S$11,$S$12,$S$13,$S$14,$S$15,$S$16,$S$17,$S$18,$S$19,$S$20)</f>
         <v>0</v>
       </c>
       <c r="T21" s="14">
+        <f>SUM($T$2,$T$3,$T$4,$T$5,$T$6,$T$7,$T$8,$T$9,$T$10,$T$11,$T$12,$T$13,$T$14,$T$15,$T$16,$T$17,$T$18,$T$19,$T$20)</f>
         <v>0</v>
       </c>
       <c r="U21" s="8">
-        <v>0</v>
+        <f>SUM($U$2,$U$3,$U$4,$U$5,$U$6,$U$7,$U$8,$U$9,$U$10,$U$11,$U$12,$U$13,$U$14,$U$15,$U$16,$U$17,$U$18,$U$19,$U$20)</f>
+        <v>78000</v>
       </c>
       <c r="V21" s="8">
-        <v>0</v>
+        <f>SUM($V$2,$V$3,$V$4,$V$5,$V$6,$V$7,$V$8,$V$9,$V$10,$V$11,$V$12,$V$13,$V$14,$V$15,$V$16,$V$17,$V$18,$V$19,$V$20)</f>
+        <v>78000</v>
       </c>
       <c r="W21" s="14">
-        <v>0</v>
+        <f>SUM($W$2,$W$3,$W$4,$W$5,$W$6,$W$7,$W$8,$W$9,$W$10,$W$11,$W$12,$W$13,$W$14,$W$15,$W$16,$W$17,$W$18,$W$19,$W$20)</f>
+        <v>78</v>
       </c>
       <c r="X21" s="14">
+        <f>SUM($X$2,$X$3,$X$4,$X$5,$X$6,$X$7,$X$8,$X$9,$X$10,$X$11,$X$12,$X$13,$X$14,$X$15,$X$16,$X$17,$X$18,$X$19,$X$20)</f>
         <v>0</v>
       </c>
       <c r="Y21" s="14">
+        <f>SUM($Y$2,$Y$3,$Y$4,$Y$5,$Y$6,$Y$7,$Y$8,$Y$9,$Y$10,$Y$11,$Y$12,$Y$13,$Y$14,$Y$15,$Y$16,$Y$17,$Y$18,$Y$19,$Y$20)</f>
         <v>0</v>
       </c>
       <c r="Z21" s="14">
+        <f>SUM($Z$2,$Z$3,$Z$4,$Z$5,$Z$6,$Z$7,$Z$8,$Z$9,$Z$10,$Z$11,$Z$12,$Z$13,$Z$14,$Z$15,$Z$16,$Z$17,$Z$18,$Z$19,$Z$20)</f>
         <v>0</v>
       </c>
       <c r="AA21" s="14">
+        <f>SUM($AA$2,$AA$3,$AA$4,$AA$5,$AA$6,$AA$7,$AA$8,$AA$9,$AA$10,$AA$11,$AA$12,$AA$13,$AA$14,$AA$15,$AA$16,$AA$17,$AA$18,$AA$19,$AA$20)</f>
         <v>0</v>
       </c>
       <c r="AB21" s="8">
-        <v>0</v>
+        <f>SUM($AB$2,$AB$3,$AB$4,$AB$5,$AB$6,$AB$7,$AB$8,$AB$9,$AB$10,$AB$11,$AB$12,$AB$13,$AB$14,$AB$15,$AB$16,$AB$17,$AB$18,$AB$19,$AB$20)</f>
+        <v>83000</v>
       </c>
       <c r="AC21" s="8">
-        <v>0</v>
+        <f>SUM($AC$2,$AC$3,$AC$4,$AC$5,$AC$6,$AC$7,$AC$8,$AC$9,$AC$10,$AC$11,$AC$12,$AC$13,$AC$14,$AC$15,$AC$16,$AC$17,$AC$18,$AC$19,$AC$20)</f>
+        <v>83000</v>
       </c>
       <c r="AD21" s="14">
-        <v>0</v>
+        <f>SUM($AD$2,$AD$3,$AD$4,$AD$5,$AD$6,$AD$7,$AD$8,$AD$9,$AD$10,$AD$11,$AD$12,$AD$13,$AD$14,$AD$15,$AD$16,$AD$17,$AD$18,$AD$19,$AD$20)</f>
+        <v>83</v>
       </c>
       <c r="AE21" s="14">
+        <f>SUM($AE$2,$AE$3,$AE$4,$AE$5,$AE$6,$AE$7,$AE$8,$AE$9,$AE$10,$AE$11,$AE$12,$AE$13,$AE$14,$AE$15,$AE$16,$AE$17,$AE$18,$AE$19,$AE$20)</f>
         <v>0</v>
       </c>
       <c r="AF21" s="14">
+        <f>SUM($AF$2,$AF$3,$AF$4,$AF$5,$AF$6,$AF$7,$AF$8,$AF$9,$AF$10,$AF$11,$AF$12,$AF$13,$AF$14,$AF$15,$AF$16,$AF$17,$AF$18,$AF$19,$AF$20)</f>
         <v>0</v>
       </c>
       <c r="AG21" s="14">
+        <f>SUM($AG$2,$AG$3,$AG$4,$AG$5,$AG$6,$AG$7,$AG$8,$AG$9,$AG$10,$AG$11,$AG$12,$AG$13,$AG$14,$AG$15,$AG$16,$AG$17,$AG$18,$AG$19,$AG$20)</f>
         <v>0</v>
       </c>
       <c r="AH21" s="8">
+        <f>SUM($AH$2,$AH$3,$AH$4,$AH$5,$AH$6,$AH$7,$AH$8,$AH$9,$AH$10,$AH$11,$AH$12,$AH$13,$AH$14,$AH$15,$AH$16,$AH$17,$AH$18,$AH$19,$AH$20)</f>
         <v>0</v>
       </c>
       <c r="AI21" s="8">
-        <v>0</v>
+        <f>SUM($AI$2,$AI$3,$AI$4,$AI$5,$AI$6,$AI$7,$AI$8,$AI$9,$AI$10,$AI$11,$AI$12,$AI$13,$AI$14,$AI$15,$AI$16,$AI$17,$AI$18,$AI$19,$AI$20)</f>
+        <v>81000</v>
       </c>
       <c r="AJ21" s="8">
-        <v>0</v>
+        <f>SUM($AJ$2,$AJ$3,$AJ$4,$AJ$5,$AJ$6,$AJ$7,$AJ$8,$AJ$9,$AJ$10,$AJ$11,$AJ$12,$AJ$13,$AJ$14,$AJ$15,$AJ$16,$AJ$17,$AJ$18,$AJ$19,$AJ$20)</f>
+        <v>81000</v>
       </c>
       <c r="AK21" s="14">
-        <v>0</v>
+        <f>SUM($AK$2,$AK$3,$AK$4,$AK$5,$AK$6,$AK$7,$AK$8,$AK$9,$AK$10,$AK$11,$AK$12,$AK$13,$AK$14,$AK$15,$AK$16,$AK$17,$AK$18,$AK$19,$AK$20)</f>
+        <v>81</v>
       </c>
       <c r="AL21" s="14">
+        <f>SUM($AL$2,$AL$3,$AL$4,$AL$5,$AL$6,$AL$7,$AL$8,$AL$9,$AL$10,$AL$11,$AL$12,$AL$13,$AL$14,$AL$15,$AL$16,$AL$17,$AL$18,$AL$19,$AL$20)</f>
         <v>0</v>
       </c>
       <c r="AM21" s="14">
+        <f>SUM($AM$2,$AM$3,$AM$4,$AM$5,$AM$6,$AM$7,$AM$8,$AM$9,$AM$10,$AM$11,$AM$12,$AM$13,$AM$14,$AM$15,$AM$16,$AM$17,$AM$18,$AM$19,$AM$20)</f>
         <v>0</v>
       </c>
       <c r="AN21" s="14">
+        <f>SUM($AN$2,$AN$3,$AN$4,$AN$5,$AN$6,$AN$7,$AN$8,$AN$9,$AN$10,$AN$11,$AN$12,$AN$13,$AN$14,$AN$15,$AN$16,$AN$17,$AN$18,$AN$19,$AN$20)</f>
         <v>0</v>
       </c>
       <c r="AO21" s="8">
+        <f>SUM($AO$2,$AO$3,$AO$4,$AO$5,$AO$6,$AO$7,$AO$8,$AO$9,$AO$10,$AO$11,$AO$12,$AO$13,$AO$14,$AO$15,$AO$16,$AO$17,$AO$18,$AO$19,$AO$20)</f>
         <v>0</v>
       </c>
       <c r="AP21" s="8">
-        <v>0</v>
+        <f>SUM($AP$2,$AP$3,$AP$4,$AP$5,$AP$6,$AP$7,$AP$8,$AP$9,$AP$10,$AP$11,$AP$12,$AP$13,$AP$14,$AP$15,$AP$16,$AP$17,$AP$18,$AP$19,$AP$20)</f>
+        <v>86000</v>
       </c>
       <c r="AQ21" s="8">
-        <v>0</v>
+        <f>SUM($AQ$2,$AQ$3,$AQ$4,$AQ$5,$AQ$6,$AQ$7,$AQ$8,$AQ$9,$AQ$10,$AQ$11,$AQ$12,$AQ$13,$AQ$14,$AQ$15,$AQ$16,$AQ$17,$AQ$18,$AQ$19,$AQ$20)</f>
+        <v>86000</v>
       </c>
       <c r="AR21" s="14">
-        <v>0</v>
+        <f>SUM($AR$2,$AR$3,$AR$4,$AR$5,$AR$6,$AR$7,$AR$8,$AR$9,$AR$10,$AR$11,$AR$12,$AR$13,$AR$14,$AR$15,$AR$16,$AR$17,$AR$18,$AR$19,$AR$20)</f>
+        <v>86</v>
       </c>
       <c r="AS21" s="14">
+        <f>SUM($AS$2,$AS$3,$AS$4,$AS$5,$AS$6,$AS$7,$AS$8,$AS$9,$AS$10,$AS$11,$AS$12,$AS$13,$AS$14,$AS$15,$AS$16,$AS$17,$AS$18,$AS$19,$AS$20)</f>
         <v>0</v>
       </c>
       <c r="AT21" s="14">
+        <f>SUM($AT$2,$AT$3,$AT$4,$AT$5,$AT$6,$AT$7,$AT$8,$AT$9,$AT$10,$AT$11,$AT$12,$AT$13,$AT$14,$AT$15,$AT$16,$AT$17,$AT$18,$AT$19,$AT$20)</f>
         <v>0</v>
       </c>
       <c r="AU21" s="14">
+        <f>SUM($AU$2,$AU$3,$AU$4,$AU$5,$AU$6,$AU$7,$AU$8,$AU$9,$AU$10,$AU$11,$AU$12,$AU$13,$AU$14,$AU$15,$AU$16,$AU$17,$AU$18,$AU$19,$AU$20)</f>
         <v>0</v>
       </c>
       <c r="AV21" s="8">
+        <f>SUM($AV$2,$AV$3,$AV$4,$AV$5,$AV$6,$AV$7,$AV$8,$AV$9,$AV$10,$AV$11,$AV$12,$AV$13,$AV$14,$AV$15,$AV$16,$AV$17,$AV$18,$AV$19,$AV$20)</f>
         <v>0</v>
       </c>
       <c r="AW21" s="8">
-        <v>0</v>
+        <f>SUM($AW$2,$AW$3,$AW$4,$AW$5,$AW$6,$AW$7,$AW$8,$AW$9,$AW$10,$AW$11,$AW$12,$AW$13,$AW$14,$AW$15,$AW$16,$AW$17,$AW$18,$AW$19,$AW$20)</f>
+        <v>85000</v>
       </c>
       <c r="AX21" s="8">
-        <v>0</v>
+        <f>SUM($AX$2,$AX$3,$AX$4,$AX$5,$AX$6,$AX$7,$AX$8,$AX$9,$AX$10,$AX$11,$AX$12,$AX$13,$AX$14,$AX$15,$AX$16,$AX$17,$AX$18,$AX$19,$AX$20)</f>
+        <v>85000</v>
       </c>
       <c r="AY21" s="14">
-        <v>0</v>
+        <f>SUM($AY$2,$AY$3,$AY$4,$AY$5,$AY$6,$AY$7,$AY$8,$AY$9,$AY$10,$AY$11,$AY$12,$AY$13,$AY$14,$AY$15,$AY$16,$AY$17,$AY$18,$AY$19,$AY$20)</f>
+        <v>85</v>
       </c>
       <c r="AZ21" s="14">
-        <v>0</v>
+        <f>SUM($AZ$2,$AZ$3,$AZ$4,$AZ$5,$AZ$6,$AZ$7,$AZ$8,$AZ$9,$AZ$10,$AZ$11,$AZ$12,$AZ$13,$AZ$14,$AZ$15,$AZ$16,$AZ$17,$AZ$18,$AZ$19,$AZ$20)</f>
+        <v>818.01</v>
       </c>
       <c r="BA21" s="14">
+        <f>SUM($BA$2,$BA$3,$BA$4,$BA$5,$BA$6,$BA$7,$BA$8,$BA$9,$BA$10,$BA$11,$BA$12,$BA$13,$BA$14,$BA$15,$BA$16,$BA$17,$BA$18,$BA$19,$BA$20)</f>
         <v>0</v>
       </c>
       <c r="BB21" s="14">
+        <f>SUM($BB$2,$BB$3,$BB$4,$BB$5,$BB$6,$BB$7,$BB$8,$BB$9,$BB$10,$BB$11,$BB$12,$BB$13,$BB$14,$BB$15,$BB$16,$BB$17,$BB$18,$BB$19,$BB$20)</f>
         <v>0</v>
       </c>
       <c r="BC21" s="8">
+        <f>SUM($BC$2,$BC$3,$BC$4,$BC$5,$BC$6,$BC$7,$BC$8,$BC$9,$BC$10,$BC$11,$BC$12,$BC$13,$BC$14,$BC$15,$BC$16,$BC$17,$BC$18,$BC$19,$BC$20)</f>
         <v>0</v>
       </c>
       <c r="BD21" s="8">
-        <v>0</v>
+        <f>SUM($BD$2,$BD$3,$BD$4,$BD$5,$BD$6,$BD$7,$BD$8,$BD$9,$BD$10,$BD$11,$BD$12,$BD$13,$BD$14,$BD$15,$BD$16,$BD$17,$BD$18,$BD$19,$BD$20)</f>
+        <v>89000</v>
       </c>
       <c r="BE21" s="8">
-        <v>0</v>
+        <f>SUM($BE$2,$BE$3,$BE$4,$BE$5,$BE$6,$BE$7,$BE$8,$BE$9,$BE$10,$BE$11,$BE$12,$BE$13,$BE$14,$BE$15,$BE$16,$BE$17,$BE$18,$BE$19,$BE$20)</f>
+        <v>89000</v>
       </c>
       <c r="BF21" s="14">
-        <v>0</v>
+        <f>SUM($BF$2,$BF$3,$BF$4,$BF$5,$BF$6,$BF$7,$BF$8,$BF$9,$BF$10,$BF$11,$BF$12,$BF$13,$BF$14,$BF$15,$BF$16,$BF$17,$BF$18,$BF$19,$BF$20)</f>
+        <v>89</v>
       </c>
       <c r="BG21" s="14">
+        <f>SUM($BG$2,$BG$3,$BG$4,$BG$5,$BG$6,$BG$7,$BG$8,$BG$9,$BG$10,$BG$11,$BG$12,$BG$13,$BG$14,$BG$15,$BG$16,$BG$17,$BG$18,$BG$19,$BG$20)</f>
         <v>0</v>
       </c>
       <c r="BH21" s="14">
+        <f>SUM($BH$2,$BH$3,$BH$4,$BH$5,$BH$6,$BH$7,$BH$8,$BH$9,$BH$10,$BH$11,$BH$12,$BH$13,$BH$14,$BH$15,$BH$16,$BH$17,$BH$18,$BH$19,$BH$20)</f>
         <v>0</v>
       </c>
       <c r="BI21" s="14">
+        <f>SUM($BI$2,$BI$3,$BI$4,$BI$5,$BI$6,$BI$7,$BI$8,$BI$9,$BI$10,$BI$11,$BI$12,$BI$13,$BI$14,$BI$15,$BI$16,$BI$17,$BI$18,$BI$19,$BI$20)</f>
         <v>0</v>
       </c>
       <c r="BJ21" s="8">
+        <f>SUM($BJ$2,$BJ$3,$BJ$4,$BJ$5,$BJ$6,$BJ$7,$BJ$8,$BJ$9,$BJ$10,$BJ$11,$BJ$12,$BJ$13,$BJ$14,$BJ$15,$BJ$16,$BJ$17,$BJ$18,$BJ$19,$BJ$20)</f>
         <v>0</v>
       </c>
       <c r="BK21" s="8">
-        <v>0</v>
+        <f>SUM($BK$2,$BK$3,$BK$4,$BK$5,$BK$6,$BK$7,$BK$8,$BK$9,$BK$10,$BK$11,$BK$12,$BK$13,$BK$14,$BK$15,$BK$16,$BK$17,$BK$18,$BK$19,$BK$20)</f>
+        <v>89000</v>
       </c>
       <c r="BL21" s="8">
-        <v>0</v>
+        <f>SUM($BL$2,$BL$3,$BL$4,$BL$5,$BL$6,$BL$7,$BL$8,$BL$9,$BL$10,$BL$11,$BL$12,$BL$13,$BL$14,$BL$15,$BL$16,$BL$17,$BL$18,$BL$19,$BL$20)</f>
+        <v>89000</v>
       </c>
       <c r="BM21" s="14">
-        <v>0</v>
+        <f>SUM($BM$2,$BM$3,$BM$4,$BM$5,$BM$6,$BM$7,$BM$8,$BM$9,$BM$10,$BM$11,$BM$12,$BM$13,$BM$14,$BM$15,$BM$16,$BM$17,$BM$18,$BM$19,$BM$20)</f>
+        <v>89</v>
       </c>
       <c r="BN21" s="14">
+        <f>SUM($BN$2,$BN$3,$BN$4,$BN$5,$BN$6,$BN$7,$BN$8,$BN$9,$BN$10,$BN$11,$BN$12,$BN$13,$BN$14,$BN$15,$BN$16,$BN$17,$BN$18,$BN$19,$BN$20)</f>
         <v>0</v>
       </c>
       <c r="BO21" s="14">
+        <f>SUM($BO$2,$BO$3,$BO$4,$BO$5,$BO$6,$BO$7,$BO$8,$BO$9,$BO$10,$BO$11,$BO$12,$BO$13,$BO$14,$BO$15,$BO$16,$BO$17,$BO$18,$BO$19,$BO$20)</f>
         <v>0</v>
       </c>
       <c r="BP21" s="8">
-        <v>0</v>
+        <f>SUM($BP$2,$BP$3,$BP$4,$BP$5,$BP$6,$BP$7,$BP$8,$BP$9,$BP$10,$BP$11,$BP$12,$BP$13,$BP$14,$BP$15,$BP$16,$BP$17,$BP$18,$BP$19,$BP$20)</f>
+        <v>80000</v>
       </c>
       <c r="BQ21" s="8">
-        <v>0</v>
+        <f>SUM($BQ$2,$BQ$3,$BQ$4,$BQ$5,$BQ$6,$BQ$7,$BQ$8,$BQ$9,$BQ$10,$BQ$11,$BQ$12,$BQ$13,$BQ$14,$BQ$15,$BQ$16,$BQ$17,$BQ$18,$BQ$19,$BQ$20)</f>
+        <v>80000</v>
       </c>
       <c r="BR21" s="14">
-        <v>0</v>
+        <f>SUM($BR$2,$BR$3,$BR$4,$BR$5,$BR$6,$BR$7,$BR$8,$BR$9,$BR$10,$BR$11,$BR$12,$BR$13,$BR$14,$BR$15,$BR$16,$BR$17,$BR$18,$BR$19,$BR$20)</f>
+        <v>80</v>
       </c>
       <c r="BS21" s="14">
+        <f>SUM($BS$2,$BS$3,$BS$4,$BS$5,$BS$6,$BS$7,$BS$8,$BS$9,$BS$10,$BS$11,$BS$12,$BS$13,$BS$14,$BS$15,$BS$16,$BS$17,$BS$18,$BS$19,$BS$20)</f>
         <v>0</v>
       </c>
       <c r="BT21" s="14">
+        <f>SUM($BT$2,$BT$3,$BT$4,$BT$5,$BT$6,$BT$7,$BT$8,$BT$9,$BT$10,$BT$11,$BT$12,$BT$13,$BT$14,$BT$15,$BT$16,$BT$17,$BT$18,$BT$19,$BT$20)</f>
         <v>0</v>
       </c>
       <c r="BU21" s="8">
-        <v>4000</v>
+        <f>SUM($BU$2,$BU$3,$BU$4,$BU$5,$BU$6,$BU$7,$BU$8,$BU$9,$BU$10,$BU$11,$BU$12,$BU$13,$BU$14,$BU$15,$BU$16,$BU$17,$BU$18,$BU$19,$BU$20)</f>
+        <v>92000</v>
       </c>
       <c r="BV21" s="8">
-        <v>4000</v>
+        <f>SUM($BV$2,$BV$3,$BV$4,$BV$5,$BV$6,$BV$7,$BV$8,$BV$9,$BV$10,$BV$11,$BV$12,$BV$13,$BV$14,$BV$15,$BV$16,$BV$17,$BV$18,$BV$19,$BV$20)</f>
+        <v>92000</v>
       </c>
       <c r="BW21" s="14">
-        <v>4</v>
+        <f>SUM($BW$2,$BW$3,$BW$4,$BW$5,$BW$6,$BW$7,$BW$8,$BW$9,$BW$10,$BW$11,$BW$12,$BW$13,$BW$14,$BW$15,$BW$16,$BW$17,$BW$18,$BW$19,$BW$20)</f>
+        <v>92</v>
       </c>
       <c r="BX21" s="14">
+        <f>SUM($BX$2,$BX$3,$BX$4,$BX$5,$BX$6,$BX$7,$BX$8,$BX$9,$BX$10,$BX$11,$BX$12,$BX$13,$BX$14,$BX$15,$BX$16,$BX$17,$BX$18,$BX$19,$BX$20)</f>
         <v>0</v>
       </c>
       <c r="BY21" s="14">
+        <f>SUM($BY$2,$BY$3,$BY$4,$BY$5,$BY$6,$BY$7,$BY$8,$BY$9,$BY$10,$BY$11,$BY$12,$BY$13,$BY$14,$BY$15,$BY$16,$BY$17,$BY$18,$BY$19,$BY$20)</f>
         <v>0</v>
       </c>
       <c r="BZ21" s="8">
-        <v>4000</v>
+        <f>SUM($BZ$2,$BZ$3,$BZ$4,$BZ$5,$BZ$6,$BZ$7,$BZ$8,$BZ$9,$BZ$10,$BZ$11,$BZ$12,$BZ$13,$BZ$14,$BZ$15,$BZ$16,$BZ$17,$BZ$18,$BZ$19,$BZ$20)</f>
+        <v>92000</v>
       </c>
       <c r="CA21" s="8">
-        <v>4000</v>
+        <f>SUM($CA$2,$CA$3,$CA$4,$CA$5,$CA$6,$CA$7,$CA$8,$CA$9,$CA$10,$CA$11,$CA$12,$CA$13,$CA$14,$CA$15,$CA$16,$CA$17,$CA$18,$CA$19,$CA$20)</f>
+        <v>92000</v>
       </c>
       <c r="CB21" s="14">
-        <v>4</v>
+        <f>SUM($CB$2,$CB$3,$CB$4,$CB$5,$CB$6,$CB$7,$CB$8,$CB$9,$CB$10,$CB$11,$CB$12,$CB$13,$CB$14,$CB$15,$CB$16,$CB$17,$CB$18,$CB$19,$CB$20)</f>
+        <v>92</v>
       </c>
       <c r="CC21" s="14">
+        <f>SUM($CC$2,$CC$3,$CC$4,$CC$5,$CC$6,$CC$7,$CC$8,$CC$9,$CC$10,$CC$11,$CC$12,$CC$13,$CC$14,$CC$15,$CC$16,$CC$17,$CC$18,$CC$19,$CC$20)</f>
         <v>0</v>
       </c>
       <c r="CD21" s="14">
+        <f>SUM($CD$2,$CD$3,$CD$4,$CD$5,$CD$6,$CD$7,$CD$8,$CD$9,$CD$10,$CD$11,$CD$12,$CD$13,$CD$14,$CD$15,$CD$16,$CD$17,$CD$18,$CD$19,$CD$20)</f>
         <v>0</v>
       </c>
       <c r="CE21" s="8">
-        <v>4000</v>
+        <f>SUM($CE$2,$CE$3,$CE$4,$CE$5,$CE$6,$CE$7,$CE$8,$CE$9,$CE$10,$CE$11,$CE$12,$CE$13,$CE$14,$CE$15,$CE$16,$CE$17,$CE$18,$CE$19,$CE$20)</f>
+        <v>92000</v>
       </c>
       <c r="CF21" s="8">
-        <v>4000</v>
+        <f>SUM($CF$2,$CF$3,$CF$4,$CF$5,$CF$6,$CF$7,$CF$8,$CF$9,$CF$10,$CF$11,$CF$12,$CF$13,$CF$14,$CF$15,$CF$16,$CF$17,$CF$18,$CF$19,$CF$20)</f>
+        <v>92000</v>
       </c>
       <c r="CG21" s="14">
-        <v>4</v>
+        <f>SUM($CG$2,$CG$3,$CG$4,$CG$5,$CG$6,$CG$7,$CG$8,$CG$9,$CG$10,$CG$11,$CG$12,$CG$13,$CG$14,$CG$15,$CG$16,$CG$17,$CG$18,$CG$19,$CG$20)</f>
+        <v>92</v>
       </c>
       <c r="CH21" s="14">
+        <f>SUM($CH$2,$CH$3,$CH$4,$CH$5,$CH$6,$CH$7,$CH$8,$CH$9,$CH$10,$CH$11,$CH$12,$CH$13,$CH$14,$CH$15,$CH$16,$CH$17,$CH$18,$CH$19,$CH$20)</f>
         <v>0</v>
       </c>
       <c r="CI21" s="14">
+        <f>SUM($CI$2,$CI$3,$CI$4,$CI$5,$CI$6,$CI$7,$CI$8,$CI$9,$CI$10,$CI$11,$CI$12,$CI$13,$CI$14,$CI$15,$CI$16,$CI$17,$CI$18,$CI$19,$CI$20)</f>
         <v>0</v>
       </c>
       <c r="CJ21" s="8">
-        <v>4000</v>
+        <f>SUM($CJ$2,$CJ$3,$CJ$4,$CJ$5,$CJ$6,$CJ$7,$CJ$8,$CJ$9,$CJ$10,$CJ$11,$CJ$12,$CJ$13,$CJ$14,$CJ$15,$CJ$16,$CJ$17,$CJ$18,$CJ$19,$CJ$20)</f>
+        <v>92000</v>
       </c>
       <c r="CK21" s="8">
-        <v>4000</v>
+        <f>SUM($CK$2,$CK$3,$CK$4,$CK$5,$CK$6,$CK$7,$CK$8,$CK$9,$CK$10,$CK$11,$CK$12,$CK$13,$CK$14,$CK$15,$CK$16,$CK$17,$CK$18,$CK$19,$CK$20)</f>
+        <v>92000</v>
       </c>
       <c r="CL21" s="14">
-        <v>4</v>
+        <f>SUM($CL$2,$CL$3,$CL$4,$CL$5,$CL$6,$CL$7,$CL$8,$CL$9,$CL$10,$CL$11,$CL$12,$CL$13,$CL$14,$CL$15,$CL$16,$CL$17,$CL$18,$CL$19,$CL$20)</f>
+        <v>92</v>
       </c>
       <c r="CM21" s="14">
+        <f>SUM($CM$2,$CM$3,$CM$4,$CM$5,$CM$6,$CM$7,$CM$8,$CM$9,$CM$10,$CM$11,$CM$12,$CM$13,$CM$14,$CM$15,$CM$16,$CM$17,$CM$18,$CM$19,$CM$20)</f>
         <v>0</v>
       </c>
       <c r="CN21" s="14">
+        <f>SUM($CN$2,$CN$3,$CN$4,$CN$5,$CN$6,$CN$7,$CN$8,$CN$9,$CN$10,$CN$11,$CN$12,$CN$13,$CN$14,$CN$15,$CN$16,$CN$17,$CN$18,$CN$19,$CN$20)</f>
         <v>0</v>
       </c>
       <c r="CO21" s="14">
+        <f>SUM($CO$2,$CO$3,$CO$4,$CO$5,$CO$6,$CO$7,$CO$8,$CO$9,$CO$10,$CO$11,$CO$12,$CO$13,$CO$14,$CO$15,$CO$16,$CO$17,$CO$18,$CO$19,$CO$20)</f>
         <v>0</v>
       </c>
       <c r="CP21" s="9">
-        <v>16000</v>
+        <f>SUM($CP$2,$CP$3,$CP$4,$CP$5,$CP$6,$CP$7,$CP$8,$CP$9,$CP$10,$CP$11,$CP$12,$CP$13,$CP$14,$CP$15,$CP$16,$CP$17,$CP$18,$CP$19,$CP$20)</f>
+        <v>1039000</v>
       </c>
       <c r="CQ21" s="9">
-        <v>16000</v>
+        <f>SUM($CQ$2,$CQ$3,$CQ$4,$CQ$5,$CQ$6,$CQ$7,$CQ$8,$CQ$9,$CQ$10,$CQ$11,$CQ$12,$CQ$13,$CQ$14,$CQ$15,$CQ$16,$CQ$17,$CQ$18,$CQ$19,$CQ$20)</f>
+        <v>1039000</v>
       </c>
       <c r="CR21" s="14">
-        <v>1.3</v>
+        <f>SUM($CR$2,$CR$3,$CR$4,$CR$5,$CR$6,$CR$7,$CR$8,$CR$9,$CR$10,$CR$11,$CR$12,$CR$13,$CR$14,$CR$15,$CR$16,$CR$17,$CR$18,$CR$19,$CR$20)</f>
+        <v>85.999999999999986</v>
       </c>
       <c r="CS21" s="14">
+        <f>SUM($CS$2,$CS$3,$CS$4,$CS$5,$CS$6,$CS$7,$CS$8,$CS$9,$CS$10,$CS$11,$CS$12,$CS$13,$CS$14,$CS$15,$CS$16,$CS$17,$CS$18,$CS$19,$CS$20)</f>
         <v>0</v>
       </c>
       <c r="CT21" s="14">
+        <f>SUM($CT$2,$CT$3,$CT$4,$CT$5,$CT$6,$CT$7,$CT$8,$CT$9,$CT$10,$CT$11,$CT$12,$CT$13,$CT$14,$CT$15,$CT$16,$CT$17,$CT$18,$CT$19,$CT$20)</f>
         <v>0</v>
       </c>
       <c r="CU21" s="14">
+        <f>SUM($CU$2,$CU$3,$CU$4,$CU$5,$CU$6,$CU$7,$CU$8,$CU$9,$CU$10,$CU$11,$CU$12,$CU$13,$CU$14,$CU$15,$CU$16,$CU$17,$CU$18,$CU$19,$CU$20)</f>
         <v>0</v>
       </c>
       <c r="CV21" s="8">
-        <v>-16000</v>
+        <f>SUM($CV$2,$CV$3,$CV$4,$CV$5,$CV$6,$CV$7,$CV$8,$CV$9,$CV$10,$CV$11,$CV$12,$CV$13,$CV$14,$CV$15,$CV$16,$CV$17,$CV$18,$CV$19,$CV$20)</f>
+        <v>-1039000</v>
       </c>
       <c r="CW21" s="8">
-        <v>-16000</v>
+        <f>SUM($CW$2,$CW$3,$CW$4,$CW$5,$CW$6,$CW$7,$CW$8,$CW$9,$CW$10,$CW$11,$CW$12,$CW$13,$CW$14,$CW$15,$CW$16,$CW$17,$CW$18,$CW$19,$CW$20)</f>
+        <v>-1039000</v>
       </c>
       <c r="CX21" s="14">
+        <f>SUM($CX$2,$CX$3,$CX$4,$CX$5,$CX$6,$CX$7,$CX$8,$CX$9,$CX$10,$CX$11,$CX$12,$CX$13,$CX$14,$CX$15,$CX$16,$CX$17,$CX$18,$CX$19,$CX$20)</f>
         <v>0</v>
       </c>
       <c r="CY21" s="14">
+        <f>SUM($CY$2,$CY$3,$CY$4,$CY$5,$CY$6,$CY$7,$CY$8,$CY$9,$CY$10,$CY$11,$CY$12,$CY$13,$CY$14,$CY$15,$CY$16,$CY$17,$CY$18,$CY$19,$CY$20)</f>
         <v>0</v>
       </c>
       <c r="CZ21" s="14">
+        <f>SUM($CZ$2,$CZ$3,$CZ$4,$CZ$5,$CZ$6,$CZ$7,$CZ$8,$CZ$9,$CZ$10,$CZ$11,$CZ$12,$CZ$13,$CZ$14,$CZ$15,$CZ$16,$CZ$17,$CZ$18,$CZ$19,$CZ$20)</f>
         <v>0</v>
       </c>
       <c r="DA21" s="14">
+        <f>SUM($DA$2,$DA$3,$DA$4,$DA$5,$DA$6,$DA$7,$DA$8,$DA$9,$DA$10,$DA$11,$DA$12,$DA$13,$DA$14,$DA$15,$DA$16,$DA$17,$DA$18,$DA$19,$DA$20)</f>
         <v>0</v>
       </c>
       <c r="DB21" s="8">
-        <v>16000</v>
+        <f>SUM($DB$2,$DB$3,$DB$4,$DB$5,$DB$6,$DB$7,$DB$8,$DB$9,$DB$10,$DB$11,$DB$12,$DB$13,$DB$14,$DB$15,$DB$16,$DB$17,$DB$18,$DB$19,$DB$20)</f>
+        <v>1039000</v>
       </c>
       <c r="DC21" s="8">
-        <v>16000</v>
+        <f>SUM($DC$2,$DC$3,$DC$4,$DC$5,$DC$6,$DC$7,$DC$8,$DC$9,$DC$10,$DC$11,$DC$12,$DC$13,$DC$14,$DC$15,$DC$16,$DC$17,$DC$18,$DC$19,$DC$20)</f>
+        <v>1039000</v>
       </c>
     </row>
     <row r="22" spans="1:107" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -7639,471 +7707,408 @@
       <c r="P22" s="6"/>
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
-      <c r="S22" s="8">
-        <f>SUM($S$2,$S$3,$S$4,$S$5,$S$6,$S$7,$S$8,$S$9,$S$10,$S$11,$S$12,$S$13,$S$14,$S$15,$S$16,$S$17,$S$18,$S$19,$S$20,$S$21)</f>
-        <v>0</v>
-      </c>
-      <c r="T22" s="8">
-        <f>SUM($T$2,$T$3,$T$4,$T$5,$T$6,$T$7,$T$8,$T$9,$T$10,$T$11,$T$12,$T$13,$T$14,$T$15,$T$16,$T$17,$T$18,$T$19,$T$20,$T$21)</f>
-        <v>0</v>
-      </c>
-      <c r="U22" s="8">
-        <f>SUM($U$2,$U$3,$U$4,$U$5,$U$6,$U$7,$U$8,$U$9,$U$10,$U$11,$U$12,$U$13,$U$14,$U$15,$U$16,$U$17,$U$18,$U$19,$U$20,$U$21)</f>
-        <v>78000</v>
-      </c>
-      <c r="V22" s="8">
-        <f>SUM($V$2,$V$3,$V$4,$V$5,$V$6,$V$7,$V$8,$V$9,$V$10,$V$11,$V$12,$V$13,$V$14,$V$15,$V$16,$V$17,$V$18,$V$19,$V$20,$V$21)</f>
-        <v>78000</v>
-      </c>
-      <c r="W22" s="8">
-        <f>SUM($W$2,$W$3,$W$4,$W$5,$W$6,$W$7,$W$8,$W$9,$W$10,$W$11,$W$12,$W$13,$W$14,$W$15,$W$16,$W$17,$W$18,$W$19,$W$20,$W$21)</f>
-        <v>78</v>
-      </c>
-      <c r="X22" s="8">
-        <f>SUM($X$2,$X$3,$X$4,$X$5,$X$6,$X$7,$X$8,$X$9,$X$10,$X$11,$X$12,$X$13,$X$14,$X$15,$X$16,$X$17,$X$18,$X$19,$X$20,$X$21)</f>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="8">
-        <f>SUM($Y$2,$Y$3,$Y$4,$Y$5,$Y$6,$Y$7,$Y$8,$Y$9,$Y$10,$Y$11,$Y$12,$Y$13,$Y$14,$Y$15,$Y$16,$Y$17,$Y$18,$Y$19,$Y$20,$Y$21)</f>
-        <v>0</v>
-      </c>
-      <c r="Z22" s="8">
-        <f>SUM($Z$2,$Z$3,$Z$4,$Z$5,$Z$6,$Z$7,$Z$8,$Z$9,$Z$10,$Z$11,$Z$12,$Z$13,$Z$14,$Z$15,$Z$16,$Z$17,$Z$18,$Z$19,$Z$20,$Z$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AA22" s="8">
-        <f>SUM($AA$2,$AA$3,$AA$4,$AA$5,$AA$6,$AA$7,$AA$8,$AA$9,$AA$10,$AA$11,$AA$12,$AA$13,$AA$14,$AA$15,$AA$16,$AA$17,$AA$18,$AA$19,$AA$20,$AA$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AB22" s="8">
-        <f>SUM($AB$2,$AB$3,$AB$4,$AB$5,$AB$6,$AB$7,$AB$8,$AB$9,$AB$10,$AB$11,$AB$12,$AB$13,$AB$14,$AB$15,$AB$16,$AB$17,$AB$18,$AB$19,$AB$20,$AB$21)</f>
-        <v>83000</v>
-      </c>
-      <c r="AC22" s="8">
-        <f>SUM($AC$2,$AC$3,$AC$4,$AC$5,$AC$6,$AC$7,$AC$8,$AC$9,$AC$10,$AC$11,$AC$12,$AC$13,$AC$14,$AC$15,$AC$16,$AC$17,$AC$18,$AC$19,$AC$20,$AC$21)</f>
-        <v>83000</v>
-      </c>
-      <c r="AD22" s="8">
-        <f>SUM($AD$2,$AD$3,$AD$4,$AD$5,$AD$6,$AD$7,$AD$8,$AD$9,$AD$10,$AD$11,$AD$12,$AD$13,$AD$14,$AD$15,$AD$16,$AD$17,$AD$18,$AD$19,$AD$20,$AD$21)</f>
-        <v>83</v>
-      </c>
-      <c r="AE22" s="8">
-        <f>SUM($AE$2,$AE$3,$AE$4,$AE$5,$AE$6,$AE$7,$AE$8,$AE$9,$AE$10,$AE$11,$AE$12,$AE$13,$AE$14,$AE$15,$AE$16,$AE$17,$AE$18,$AE$19,$AE$20,$AE$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AF22" s="8">
-        <f>SUM($AF$2,$AF$3,$AF$4,$AF$5,$AF$6,$AF$7,$AF$8,$AF$9,$AF$10,$AF$11,$AF$12,$AF$13,$AF$14,$AF$15,$AF$16,$AF$17,$AF$18,$AF$19,$AF$20,$AF$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AG22" s="8">
-        <f>SUM($AG$2,$AG$3,$AG$4,$AG$5,$AG$6,$AG$7,$AG$8,$AG$9,$AG$10,$AG$11,$AG$12,$AG$13,$AG$14,$AG$15,$AG$16,$AG$17,$AG$18,$AG$19,$AG$20,$AG$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AH22" s="8">
-        <f>SUM($AH$2,$AH$3,$AH$4,$AH$5,$AH$6,$AH$7,$AH$8,$AH$9,$AH$10,$AH$11,$AH$12,$AH$13,$AH$14,$AH$15,$AH$16,$AH$17,$AH$18,$AH$19,$AH$20,$AH$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AI22" s="8">
-        <f>SUM($AI$2,$AI$3,$AI$4,$AI$5,$AI$6,$AI$7,$AI$8,$AI$9,$AI$10,$AI$11,$AI$12,$AI$13,$AI$14,$AI$15,$AI$16,$AI$17,$AI$18,$AI$19,$AI$20,$AI$21)</f>
-        <v>83000</v>
-      </c>
-      <c r="AJ22" s="8">
-        <f>SUM($AJ$2,$AJ$3,$AJ$4,$AJ$5,$AJ$6,$AJ$7,$AJ$8,$AJ$9,$AJ$10,$AJ$11,$AJ$12,$AJ$13,$AJ$14,$AJ$15,$AJ$16,$AJ$17,$AJ$18,$AJ$19,$AJ$20,$AJ$21)</f>
-        <v>83000</v>
-      </c>
-      <c r="AK22" s="8">
-        <f>SUM($AK$2,$AK$3,$AK$4,$AK$5,$AK$6,$AK$7,$AK$8,$AK$9,$AK$10,$AK$11,$AK$12,$AK$13,$AK$14,$AK$15,$AK$16,$AK$17,$AK$18,$AK$19,$AK$20,$AK$21)</f>
-        <v>83</v>
-      </c>
-      <c r="AL22" s="8">
-        <f>SUM($AL$2,$AL$3,$AL$4,$AL$5,$AL$6,$AL$7,$AL$8,$AL$9,$AL$10,$AL$11,$AL$12,$AL$13,$AL$14,$AL$15,$AL$16,$AL$17,$AL$18,$AL$19,$AL$20,$AL$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AM22" s="8">
-        <f>SUM($AM$2,$AM$3,$AM$4,$AM$5,$AM$6,$AM$7,$AM$8,$AM$9,$AM$10,$AM$11,$AM$12,$AM$13,$AM$14,$AM$15,$AM$16,$AM$17,$AM$18,$AM$19,$AM$20,$AM$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AN22" s="8">
-        <f>SUM($AN$2,$AN$3,$AN$4,$AN$5,$AN$6,$AN$7,$AN$8,$AN$9,$AN$10,$AN$11,$AN$12,$AN$13,$AN$14,$AN$15,$AN$16,$AN$17,$AN$18,$AN$19,$AN$20,$AN$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AO22" s="8">
-        <f>SUM($AO$2,$AO$3,$AO$4,$AO$5,$AO$6,$AO$7,$AO$8,$AO$9,$AO$10,$AO$11,$AO$12,$AO$13,$AO$14,$AO$15,$AO$16,$AO$17,$AO$18,$AO$19,$AO$20,$AO$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AP22" s="8">
-        <f>SUM($AP$2,$AP$3,$AP$4,$AP$5,$AP$6,$AP$7,$AP$8,$AP$9,$AP$10,$AP$11,$AP$12,$AP$13,$AP$14,$AP$15,$AP$16,$AP$17,$AP$18,$AP$19,$AP$20,$AP$21)</f>
-        <v>89000</v>
-      </c>
-      <c r="AQ22" s="8">
-        <f>SUM($AQ$2,$AQ$3,$AQ$4,$AQ$5,$AQ$6,$AQ$7,$AQ$8,$AQ$9,$AQ$10,$AQ$11,$AQ$12,$AQ$13,$AQ$14,$AQ$15,$AQ$16,$AQ$17,$AQ$18,$AQ$19,$AQ$20,$AQ$21)</f>
-        <v>89000</v>
-      </c>
-      <c r="AR22" s="8">
-        <f>SUM($AR$2,$AR$3,$AR$4,$AR$5,$AR$6,$AR$7,$AR$8,$AR$9,$AR$10,$AR$11,$AR$12,$AR$13,$AR$14,$AR$15,$AR$16,$AR$17,$AR$18,$AR$19,$AR$20,$AR$21)</f>
-        <v>89</v>
-      </c>
-      <c r="AS22" s="8">
-        <f>SUM($AS$2,$AS$3,$AS$4,$AS$5,$AS$6,$AS$7,$AS$8,$AS$9,$AS$10,$AS$11,$AS$12,$AS$13,$AS$14,$AS$15,$AS$16,$AS$17,$AS$18,$AS$19,$AS$20,$AS$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AT22" s="8">
-        <f>SUM($AT$2,$AT$3,$AT$4,$AT$5,$AT$6,$AT$7,$AT$8,$AT$9,$AT$10,$AT$11,$AT$12,$AT$13,$AT$14,$AT$15,$AT$16,$AT$17,$AT$18,$AT$19,$AT$20,$AT$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AU22" s="8">
-        <f>SUM($AU$2,$AU$3,$AU$4,$AU$5,$AU$6,$AU$7,$AU$8,$AU$9,$AU$10,$AU$11,$AU$12,$AU$13,$AU$14,$AU$15,$AU$16,$AU$17,$AU$18,$AU$19,$AU$20,$AU$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AV22" s="8">
-        <f>SUM($AV$2,$AV$3,$AV$4,$AV$5,$AV$6,$AV$7,$AV$8,$AV$9,$AV$10,$AV$11,$AV$12,$AV$13,$AV$14,$AV$15,$AV$16,$AV$17,$AV$18,$AV$19,$AV$20,$AV$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AW22" s="8">
-        <f>SUM($AW$2,$AW$3,$AW$4,$AW$5,$AW$6,$AW$7,$AW$8,$AW$9,$AW$10,$AW$11,$AW$12,$AW$13,$AW$14,$AW$15,$AW$16,$AW$17,$AW$18,$AW$19,$AW$20,$AW$21)</f>
-        <v>89000</v>
-      </c>
-      <c r="AX22" s="8">
-        <f>SUM($AX$2,$AX$3,$AX$4,$AX$5,$AX$6,$AX$7,$AX$8,$AX$9,$AX$10,$AX$11,$AX$12,$AX$13,$AX$14,$AX$15,$AX$16,$AX$17,$AX$18,$AX$19,$AX$20,$AX$21)</f>
-        <v>89000</v>
-      </c>
-      <c r="AY22" s="8">
-        <f>SUM($AY$2,$AY$3,$AY$4,$AY$5,$AY$6,$AY$7,$AY$8,$AY$9,$AY$10,$AY$11,$AY$12,$AY$13,$AY$14,$AY$15,$AY$16,$AY$17,$AY$18,$AY$19,$AY$20,$AY$21)</f>
-        <v>89</v>
-      </c>
-      <c r="AZ22" s="8">
-        <f>SUM($AZ$2,$AZ$3,$AZ$4,$AZ$5,$AZ$6,$AZ$7,$AZ$8,$AZ$9,$AZ$10,$AZ$11,$AZ$12,$AZ$13,$AZ$14,$AZ$15,$AZ$16,$AZ$17,$AZ$18,$AZ$19,$AZ$20,$AZ$21)</f>
-        <v>818.01</v>
-      </c>
-      <c r="BA22" s="8">
-        <f>SUM($BA$2,$BA$3,$BA$4,$BA$5,$BA$6,$BA$7,$BA$8,$BA$9,$BA$10,$BA$11,$BA$12,$BA$13,$BA$14,$BA$15,$BA$16,$BA$17,$BA$18,$BA$19,$BA$20,$BA$21)</f>
-        <v>0</v>
-      </c>
-      <c r="BB22" s="8">
-        <f>SUM($BB$2,$BB$3,$BB$4,$BB$5,$BB$6,$BB$7,$BB$8,$BB$9,$BB$10,$BB$11,$BB$12,$BB$13,$BB$14,$BB$15,$BB$16,$BB$17,$BB$18,$BB$19,$BB$20,$BB$21)</f>
-        <v>0</v>
-      </c>
-      <c r="BC22" s="8">
-        <f>SUM($BC$2,$BC$3,$BC$4,$BC$5,$BC$6,$BC$7,$BC$8,$BC$9,$BC$10,$BC$11,$BC$12,$BC$13,$BC$14,$BC$15,$BC$16,$BC$17,$BC$18,$BC$19,$BC$20,$BC$21)</f>
-        <v>0</v>
-      </c>
-      <c r="BD22" s="8">
-        <f>SUM($BD$2,$BD$3,$BD$4,$BD$5,$BD$6,$BD$7,$BD$8,$BD$9,$BD$10,$BD$11,$BD$12,$BD$13,$BD$14,$BD$15,$BD$16,$BD$17,$BD$18,$BD$19,$BD$20,$BD$21)</f>
-        <v>93000</v>
-      </c>
-      <c r="BE22" s="8">
-        <f>SUM($BE$2,$BE$3,$BE$4,$BE$5,$BE$6,$BE$7,$BE$8,$BE$9,$BE$10,$BE$11,$BE$12,$BE$13,$BE$14,$BE$15,$BE$16,$BE$17,$BE$18,$BE$19,$BE$20,$BE$21)</f>
-        <v>93000</v>
-      </c>
-      <c r="BF22" s="8">
-        <f>SUM($BF$2,$BF$3,$BF$4,$BF$5,$BF$6,$BF$7,$BF$8,$BF$9,$BF$10,$BF$11,$BF$12,$BF$13,$BF$14,$BF$15,$BF$16,$BF$17,$BF$18,$BF$19,$BF$20,$BF$21)</f>
-        <v>93</v>
-      </c>
-      <c r="BG22" s="8">
-        <f>SUM($BG$2,$BG$3,$BG$4,$BG$5,$BG$6,$BG$7,$BG$8,$BG$9,$BG$10,$BG$11,$BG$12,$BG$13,$BG$14,$BG$15,$BG$16,$BG$17,$BG$18,$BG$19,$BG$20,$BG$21)</f>
-        <v>0</v>
-      </c>
-      <c r="BH22" s="8">
-        <f>SUM($BH$2,$BH$3,$BH$4,$BH$5,$BH$6,$BH$7,$BH$8,$BH$9,$BH$10,$BH$11,$BH$12,$BH$13,$BH$14,$BH$15,$BH$16,$BH$17,$BH$18,$BH$19,$BH$20,$BH$21)</f>
-        <v>0</v>
-      </c>
-      <c r="BI22" s="8">
-        <f>SUM($BI$2,$BI$3,$BI$4,$BI$5,$BI$6,$BI$7,$BI$8,$BI$9,$BI$10,$BI$11,$BI$12,$BI$13,$BI$14,$BI$15,$BI$16,$BI$17,$BI$18,$BI$19,$BI$20,$BI$21)</f>
-        <v>0</v>
-      </c>
-      <c r="BJ22" s="8">
-        <f>SUM($BJ$2,$BJ$3,$BJ$4,$BJ$5,$BJ$6,$BJ$7,$BJ$8,$BJ$9,$BJ$10,$BJ$11,$BJ$12,$BJ$13,$BJ$14,$BJ$15,$BJ$16,$BJ$17,$BJ$18,$BJ$19,$BJ$20,$BJ$21)</f>
-        <v>0</v>
-      </c>
-      <c r="BK22" s="8">
-        <f>SUM($BK$2,$BK$3,$BK$4,$BK$5,$BK$6,$BK$7,$BK$8,$BK$9,$BK$10,$BK$11,$BK$12,$BK$13,$BK$14,$BK$15,$BK$16,$BK$17,$BK$18,$BK$19,$BK$20,$BK$21)</f>
-        <v>93000</v>
-      </c>
-      <c r="BL22" s="8">
-        <f>SUM($BL$2,$BL$3,$BL$4,$BL$5,$BL$6,$BL$7,$BL$8,$BL$9,$BL$10,$BL$11,$BL$12,$BL$13,$BL$14,$BL$15,$BL$16,$BL$17,$BL$18,$BL$19,$BL$20,$BL$21)</f>
-        <v>93000</v>
-      </c>
-      <c r="BM22" s="8">
-        <f>SUM($BM$2,$BM$3,$BM$4,$BM$5,$BM$6,$BM$7,$BM$8,$BM$9,$BM$10,$BM$11,$BM$12,$BM$13,$BM$14,$BM$15,$BM$16,$BM$17,$BM$18,$BM$19,$BM$20,$BM$21)</f>
-        <v>93</v>
-      </c>
-      <c r="BN22" s="8">
-        <f>SUM($BN$2,$BN$3,$BN$4,$BN$5,$BN$6,$BN$7,$BN$8,$BN$9,$BN$10,$BN$11,$BN$12,$BN$13,$BN$14,$BN$15,$BN$16,$BN$17,$BN$18,$BN$19,$BN$20,$BN$21)</f>
-        <v>0</v>
-      </c>
-      <c r="BO22" s="8">
-        <f>SUM($BO$2,$BO$3,$BO$4,$BO$5,$BO$6,$BO$7,$BO$8,$BO$9,$BO$10,$BO$11,$BO$12,$BO$13,$BO$14,$BO$15,$BO$16,$BO$17,$BO$18,$BO$19,$BO$20,$BO$21)</f>
-        <v>0</v>
-      </c>
-      <c r="BP22" s="8">
-        <f>SUM($BP$2,$BP$3,$BP$4,$BP$5,$BP$6,$BP$7,$BP$8,$BP$9,$BP$10,$BP$11,$BP$12,$BP$13,$BP$14,$BP$15,$BP$16,$BP$17,$BP$18,$BP$19,$BP$20,$BP$21)</f>
-        <v>84000</v>
-      </c>
-      <c r="BQ22" s="8">
-        <f>SUM($BQ$2,$BQ$3,$BQ$4,$BQ$5,$BQ$6,$BQ$7,$BQ$8,$BQ$9,$BQ$10,$BQ$11,$BQ$12,$BQ$13,$BQ$14,$BQ$15,$BQ$16,$BQ$17,$BQ$18,$BQ$19,$BQ$20,$BQ$21)</f>
-        <v>84000</v>
-      </c>
-      <c r="BR22" s="8">
-        <f>SUM($BR$2,$BR$3,$BR$4,$BR$5,$BR$6,$BR$7,$BR$8,$BR$9,$BR$10,$BR$11,$BR$12,$BR$13,$BR$14,$BR$15,$BR$16,$BR$17,$BR$18,$BR$19,$BR$20,$BR$21)</f>
-        <v>84</v>
-      </c>
-      <c r="BS22" s="8">
-        <f>SUM($BS$2,$BS$3,$BS$4,$BS$5,$BS$6,$BS$7,$BS$8,$BS$9,$BS$10,$BS$11,$BS$12,$BS$13,$BS$14,$BS$15,$BS$16,$BS$17,$BS$18,$BS$19,$BS$20,$BS$21)</f>
-        <v>0</v>
-      </c>
-      <c r="BT22" s="8">
-        <f>SUM($BT$2,$BT$3,$BT$4,$BT$5,$BT$6,$BT$7,$BT$8,$BT$9,$BT$10,$BT$11,$BT$12,$BT$13,$BT$14,$BT$15,$BT$16,$BT$17,$BT$18,$BT$19,$BT$20,$BT$21)</f>
-        <v>0</v>
-      </c>
-      <c r="BU22" s="8">
-        <f>SUM($BU$2,$BU$3,$BU$4,$BU$5,$BU$6,$BU$7,$BU$8,$BU$9,$BU$10,$BU$11,$BU$12,$BU$13,$BU$14,$BU$15,$BU$16,$BU$17,$BU$18,$BU$19,$BU$20,$BU$21)</f>
-        <v>96000</v>
-      </c>
-      <c r="BV22" s="8">
-        <f>SUM($BV$2,$BV$3,$BV$4,$BV$5,$BV$6,$BV$7,$BV$8,$BV$9,$BV$10,$BV$11,$BV$12,$BV$13,$BV$14,$BV$15,$BV$16,$BV$17,$BV$18,$BV$19,$BV$20,$BV$21)</f>
-        <v>96000</v>
-      </c>
-      <c r="BW22" s="8">
-        <f>SUM($BW$2,$BW$3,$BW$4,$BW$5,$BW$6,$BW$7,$BW$8,$BW$9,$BW$10,$BW$11,$BW$12,$BW$13,$BW$14,$BW$15,$BW$16,$BW$17,$BW$18,$BW$19,$BW$20,$BW$21)</f>
-        <v>96</v>
-      </c>
-      <c r="BX22" s="8">
-        <f>SUM($BX$2,$BX$3,$BX$4,$BX$5,$BX$6,$BX$7,$BX$8,$BX$9,$BX$10,$BX$11,$BX$12,$BX$13,$BX$14,$BX$15,$BX$16,$BX$17,$BX$18,$BX$19,$BX$20,$BX$21)</f>
-        <v>0</v>
-      </c>
-      <c r="BY22" s="8">
-        <f>SUM($BY$2,$BY$3,$BY$4,$BY$5,$BY$6,$BY$7,$BY$8,$BY$9,$BY$10,$BY$11,$BY$12,$BY$13,$BY$14,$BY$15,$BY$16,$BY$17,$BY$18,$BY$19,$BY$20,$BY$21)</f>
-        <v>0</v>
-      </c>
-      <c r="BZ22" s="8">
-        <f>SUM($BZ$2,$BZ$3,$BZ$4,$BZ$5,$BZ$6,$BZ$7,$BZ$8,$BZ$9,$BZ$10,$BZ$11,$BZ$12,$BZ$13,$BZ$14,$BZ$15,$BZ$16,$BZ$17,$BZ$18,$BZ$19,$BZ$20,$BZ$21)</f>
-        <v>96000</v>
-      </c>
-      <c r="CA22" s="8">
-        <f>SUM($CA$2,$CA$3,$CA$4,$CA$5,$CA$6,$CA$7,$CA$8,$CA$9,$CA$10,$CA$11,$CA$12,$CA$13,$CA$14,$CA$15,$CA$16,$CA$17,$CA$18,$CA$19,$CA$20,$CA$21)</f>
-        <v>96000</v>
-      </c>
-      <c r="CB22" s="8">
-        <f>SUM($CB$2,$CB$3,$CB$4,$CB$5,$CB$6,$CB$7,$CB$8,$CB$9,$CB$10,$CB$11,$CB$12,$CB$13,$CB$14,$CB$15,$CB$16,$CB$17,$CB$18,$CB$19,$CB$20,$CB$21)</f>
-        <v>96</v>
-      </c>
-      <c r="CC22" s="8">
-        <f>SUM($CC$2,$CC$3,$CC$4,$CC$5,$CC$6,$CC$7,$CC$8,$CC$9,$CC$10,$CC$11,$CC$12,$CC$13,$CC$14,$CC$15,$CC$16,$CC$17,$CC$18,$CC$19,$CC$20,$CC$21)</f>
-        <v>0</v>
-      </c>
-      <c r="CD22" s="8">
-        <f>SUM($CD$2,$CD$3,$CD$4,$CD$5,$CD$6,$CD$7,$CD$8,$CD$9,$CD$10,$CD$11,$CD$12,$CD$13,$CD$14,$CD$15,$CD$16,$CD$17,$CD$18,$CD$19,$CD$20,$CD$21)</f>
-        <v>0</v>
-      </c>
-      <c r="CE22" s="8">
-        <f>SUM($CE$2,$CE$3,$CE$4,$CE$5,$CE$6,$CE$7,$CE$8,$CE$9,$CE$10,$CE$11,$CE$12,$CE$13,$CE$14,$CE$15,$CE$16,$CE$17,$CE$18,$CE$19,$CE$20,$CE$21)</f>
-        <v>96000</v>
-      </c>
-      <c r="CF22" s="8">
-        <f>SUM($CF$2,$CF$3,$CF$4,$CF$5,$CF$6,$CF$7,$CF$8,$CF$9,$CF$10,$CF$11,$CF$12,$CF$13,$CF$14,$CF$15,$CF$16,$CF$17,$CF$18,$CF$19,$CF$20,$CF$21)</f>
-        <v>96000</v>
-      </c>
-      <c r="CG22" s="8">
-        <f>SUM($CG$2,$CG$3,$CG$4,$CG$5,$CG$6,$CG$7,$CG$8,$CG$9,$CG$10,$CG$11,$CG$12,$CG$13,$CG$14,$CG$15,$CG$16,$CG$17,$CG$18,$CG$19,$CG$20,$CG$21)</f>
-        <v>96</v>
-      </c>
-      <c r="CH22" s="8">
-        <f>SUM($CH$2,$CH$3,$CH$4,$CH$5,$CH$6,$CH$7,$CH$8,$CH$9,$CH$10,$CH$11,$CH$12,$CH$13,$CH$14,$CH$15,$CH$16,$CH$17,$CH$18,$CH$19,$CH$20,$CH$21)</f>
-        <v>0</v>
-      </c>
-      <c r="CI22" s="8">
-        <f>SUM($CI$2,$CI$3,$CI$4,$CI$5,$CI$6,$CI$7,$CI$8,$CI$9,$CI$10,$CI$11,$CI$12,$CI$13,$CI$14,$CI$15,$CI$16,$CI$17,$CI$18,$CI$19,$CI$20,$CI$21)</f>
-        <v>0</v>
-      </c>
-      <c r="CJ22" s="8">
-        <f>SUM($CJ$2,$CJ$3,$CJ$4,$CJ$5,$CJ$6,$CJ$7,$CJ$8,$CJ$9,$CJ$10,$CJ$11,$CJ$12,$CJ$13,$CJ$14,$CJ$15,$CJ$16,$CJ$17,$CJ$18,$CJ$19,$CJ$20,$CJ$21)</f>
-        <v>96000</v>
-      </c>
-      <c r="CK22" s="8">
-        <f>SUM($CK$2,$CK$3,$CK$4,$CK$5,$CK$6,$CK$7,$CK$8,$CK$9,$CK$10,$CK$11,$CK$12,$CK$13,$CK$14,$CK$15,$CK$16,$CK$17,$CK$18,$CK$19,$CK$20,$CK$21)</f>
-        <v>96000</v>
-      </c>
-      <c r="CL22" s="8">
-        <f>SUM($CL$2,$CL$3,$CL$4,$CL$5,$CL$6,$CL$7,$CL$8,$CL$9,$CL$10,$CL$11,$CL$12,$CL$13,$CL$14,$CL$15,$CL$16,$CL$17,$CL$18,$CL$19,$CL$20,$CL$21)</f>
-        <v>96</v>
-      </c>
-      <c r="CM22" s="8">
-        <f>SUM($CM$2,$CM$3,$CM$4,$CM$5,$CM$6,$CM$7,$CM$8,$CM$9,$CM$10,$CM$11,$CM$12,$CM$13,$CM$14,$CM$15,$CM$16,$CM$17,$CM$18,$CM$19,$CM$20,$CM$21)</f>
-        <v>0</v>
-      </c>
-      <c r="CN22" s="8">
-        <f>SUM($CN$2,$CN$3,$CN$4,$CN$5,$CN$6,$CN$7,$CN$8,$CN$9,$CN$10,$CN$11,$CN$12,$CN$13,$CN$14,$CN$15,$CN$16,$CN$17,$CN$18,$CN$19,$CN$20,$CN$21)</f>
-        <v>0</v>
-      </c>
-      <c r="CO22" s="8">
-        <f>SUM($CO$2,$CO$3,$CO$4,$CO$5,$CO$6,$CO$7,$CO$8,$CO$9,$CO$10,$CO$11,$CO$12,$CO$13,$CO$14,$CO$15,$CO$16,$CO$17,$CO$18,$CO$19,$CO$20,$CO$21)</f>
-        <v>0</v>
-      </c>
-      <c r="CP22" s="9">
-        <f>SUM($CP$2,$CP$3,$CP$4,$CP$5,$CP$6,$CP$7,$CP$8,$CP$9,$CP$10,$CP$11,$CP$12,$CP$13,$CP$14,$CP$15,$CP$16,$CP$17,$CP$18,$CP$19,$CP$20,$CP$21)</f>
-        <v>1076000</v>
-      </c>
-      <c r="CQ22" s="9">
-        <f>SUM($CQ$2,$CQ$3,$CQ$4,$CQ$5,$CQ$6,$CQ$7,$CQ$8,$CQ$9,$CQ$10,$CQ$11,$CQ$12,$CQ$13,$CQ$14,$CQ$15,$CQ$16,$CQ$17,$CQ$18,$CQ$19,$CQ$20,$CQ$21)</f>
-        <v>1076000</v>
-      </c>
-      <c r="CR22" s="8">
-        <f>SUM($CR$2,$CR$3,$CR$4,$CR$5,$CR$6,$CR$7,$CR$8,$CR$9,$CR$10,$CR$11,$CR$12,$CR$13,$CR$14,$CR$15,$CR$16,$CR$17,$CR$18,$CR$19,$CR$20,$CR$21)</f>
-        <v>89.09999999999998</v>
-      </c>
-      <c r="CS22" s="8">
-        <f>SUM($CS$2,$CS$3,$CS$4,$CS$5,$CS$6,$CS$7,$CS$8,$CS$9,$CS$10,$CS$11,$CS$12,$CS$13,$CS$14,$CS$15,$CS$16,$CS$17,$CS$18,$CS$19,$CS$20,$CS$21)</f>
-        <v>0</v>
-      </c>
-      <c r="CT22" s="8">
-        <f>SUM($CT$2,$CT$3,$CT$4,$CT$5,$CT$6,$CT$7,$CT$8,$CT$9,$CT$10,$CT$11,$CT$12,$CT$13,$CT$14,$CT$15,$CT$16,$CT$17,$CT$18,$CT$19,$CT$20,$CT$21)</f>
-        <v>0</v>
-      </c>
-      <c r="CU22" s="8">
-        <f>SUM($CU$2,$CU$3,$CU$4,$CU$5,$CU$6,$CU$7,$CU$8,$CU$9,$CU$10,$CU$11,$CU$12,$CU$13,$CU$14,$CU$15,$CU$16,$CU$17,$CU$18,$CU$19,$CU$20,$CU$21)</f>
-        <v>0</v>
-      </c>
-      <c r="CV22" s="8">
-        <f>SUM($CV$2,$CV$3,$CV$4,$CV$5,$CV$6,$CV$7,$CV$8,$CV$9,$CV$10,$CV$11,$CV$12,$CV$13,$CV$14,$CV$15,$CV$16,$CV$17,$CV$18,$CV$19,$CV$20,$CV$21)</f>
-        <v>-1076000</v>
-      </c>
-      <c r="CW22" s="8">
-        <f>SUM($CW$2,$CW$3,$CW$4,$CW$5,$CW$6,$CW$7,$CW$8,$CW$9,$CW$10,$CW$11,$CW$12,$CW$13,$CW$14,$CW$15,$CW$16,$CW$17,$CW$18,$CW$19,$CW$20,$CW$21)</f>
-        <v>-1076000</v>
-      </c>
-      <c r="CX22" s="8">
-        <f>SUM($CX$2,$CX$3,$CX$4,$CX$5,$CX$6,$CX$7,$CX$8,$CX$9,$CX$10,$CX$11,$CX$12,$CX$13,$CX$14,$CX$15,$CX$16,$CX$17,$CX$18,$CX$19,$CX$20,$CX$21)</f>
-        <v>0</v>
-      </c>
-      <c r="CY22" s="8">
-        <f>SUM($CY$2,$CY$3,$CY$4,$CY$5,$CY$6,$CY$7,$CY$8,$CY$9,$CY$10,$CY$11,$CY$12,$CY$13,$CY$14,$CY$15,$CY$16,$CY$17,$CY$18,$CY$19,$CY$20,$CY$21)</f>
-        <v>0</v>
-      </c>
-      <c r="CZ22" s="8">
-        <f>SUM($CZ$2,$CZ$3,$CZ$4,$CZ$5,$CZ$6,$CZ$7,$CZ$8,$CZ$9,$CZ$10,$CZ$11,$CZ$12,$CZ$13,$CZ$14,$CZ$15,$CZ$16,$CZ$17,$CZ$18,$CZ$19,$CZ$20,$CZ$21)</f>
-        <v>0</v>
-      </c>
-      <c r="DA22" s="8">
-        <f>SUM($DA$2,$DA$3,$DA$4,$DA$5,$DA$6,$DA$7,$DA$8,$DA$9,$DA$10,$DA$11,$DA$12,$DA$13,$DA$14,$DA$15,$DA$16,$DA$17,$DA$18,$DA$19,$DA$20,$DA$21)</f>
-        <v>0</v>
-      </c>
-      <c r="DB22" s="8">
-        <f>SUM($DB$2,$DB$3,$DB$4,$DB$5,$DB$6,$DB$7,$DB$8,$DB$9,$DB$10,$DB$11,$DB$12,$DB$13,$DB$14,$DB$15,$DB$16,$DB$17,$DB$18,$DB$19,$DB$20,$DB$21)</f>
-        <v>1076000</v>
-      </c>
-      <c r="DC22" s="8">
-        <f>SUM($DC$2,$DC$3,$DC$4,$DC$5,$DC$6,$DC$7,$DC$8,$DC$9,$DC$10,$DC$11,$DC$12,$DC$13,$DC$14,$DC$15,$DC$16,$DC$17,$DC$18,$DC$19,$DC$20,$DC$21)</f>
-        <v>1076000</v>
-      </c>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8"/>
+      <c r="X22" s="8"/>
+      <c r="Y22" s="8"/>
+      <c r="Z22" s="8"/>
+      <c r="AA22" s="8"/>
+      <c r="AB22" s="8"/>
+      <c r="AC22" s="8"/>
+      <c r="AD22" s="8"/>
+      <c r="AE22" s="8"/>
+      <c r="AF22" s="8"/>
+      <c r="AG22" s="8"/>
+      <c r="AH22" s="8"/>
+      <c r="AI22" s="8"/>
+      <c r="AJ22" s="8"/>
+      <c r="AK22" s="8"/>
+      <c r="AL22" s="8"/>
+      <c r="AM22" s="8"/>
+      <c r="AN22" s="8"/>
+      <c r="AO22" s="8"/>
+      <c r="AP22" s="8"/>
+      <c r="AQ22" s="8"/>
+      <c r="AR22" s="8"/>
+      <c r="AS22" s="8"/>
+      <c r="AT22" s="8"/>
+      <c r="AU22" s="8"/>
+      <c r="AV22" s="8"/>
+      <c r="AW22" s="8"/>
+      <c r="AX22" s="8"/>
+      <c r="AY22" s="8"/>
+      <c r="AZ22" s="8"/>
+      <c r="BA22" s="8"/>
+      <c r="BB22" s="8"/>
+      <c r="BC22" s="8"/>
+      <c r="BD22" s="8"/>
+      <c r="BE22" s="8"/>
+      <c r="BF22" s="8"/>
+      <c r="BG22" s="8"/>
+      <c r="BH22" s="8"/>
+      <c r="BI22" s="8"/>
+      <c r="BJ22" s="8"/>
+      <c r="BK22" s="8"/>
+      <c r="BL22" s="8"/>
+      <c r="BM22" s="8"/>
+      <c r="BN22" s="8"/>
+      <c r="BO22" s="8"/>
+      <c r="BP22" s="8"/>
+      <c r="BQ22" s="8"/>
+      <c r="BR22" s="8"/>
+      <c r="BS22" s="8"/>
+      <c r="BT22" s="8"/>
+      <c r="BU22" s="8"/>
+      <c r="BV22" s="8"/>
+      <c r="BW22" s="8"/>
+      <c r="BX22" s="8"/>
+      <c r="BY22" s="8"/>
+      <c r="BZ22" s="8"/>
+      <c r="CA22" s="8"/>
+      <c r="CB22" s="8"/>
+      <c r="CC22" s="8"/>
+      <c r="CD22" s="8"/>
+      <c r="CE22" s="8"/>
+      <c r="CF22" s="8"/>
+      <c r="CG22" s="8"/>
+      <c r="CH22" s="8"/>
+      <c r="CI22" s="8"/>
+      <c r="CJ22" s="8"/>
+      <c r="CK22" s="8"/>
+      <c r="CL22" s="8"/>
+      <c r="CM22" s="8"/>
+      <c r="CN22" s="8"/>
+      <c r="CO22" s="8"/>
+      <c r="CP22" s="9"/>
+      <c r="CQ22" s="9"/>
+      <c r="CR22" s="8"/>
+      <c r="CS22" s="8"/>
+      <c r="CT22" s="8"/>
+      <c r="CU22" s="8"/>
+      <c r="CV22" s="8"/>
+      <c r="CW22" s="8"/>
+      <c r="CX22" s="8"/>
+      <c r="CY22" s="8"/>
+      <c r="CZ22" s="8"/>
+      <c r="DA22" s="8"/>
+      <c r="DB22" s="8"/>
+      <c r="DC22" s="8"/>
     </row>
     <row r="23" spans="1:107" x14ac:dyDescent="0.3">
-      <c r="A23" s="10"/>
+      <c r="A23" s="10" t="s">
+        <v>127</v>
+      </c>
       <c r="B23" s="10"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="C23" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>167</v>
+      </c>
       <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="12"/>
+      <c r="H23" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="I23" s="11">
+        <v>5842263202</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="N23" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="O23" s="12" t="s">
+        <v>114</v>
+      </c>
       <c r="P23" s="12"/>
       <c r="Q23" s="13"/>
       <c r="R23" s="13"/>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
-      <c r="U23" s="8"/>
-      <c r="V23" s="8"/>
-      <c r="W23" s="14"/>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="14"/>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="14"/>
-      <c r="AB23" s="8"/>
-      <c r="AC23" s="8"/>
-      <c r="AD23" s="14"/>
-      <c r="AE23" s="14"/>
-      <c r="AF23" s="14"/>
-      <c r="AG23" s="14"/>
-      <c r="AH23" s="8"/>
-      <c r="AI23" s="8"/>
-      <c r="AJ23" s="8"/>
-      <c r="AK23" s="14"/>
-      <c r="AL23" s="14"/>
-      <c r="AM23" s="14"/>
-      <c r="AN23" s="14"/>
-      <c r="AO23" s="8"/>
-      <c r="AP23" s="8"/>
-      <c r="AQ23" s="8"/>
-      <c r="AR23" s="14"/>
-      <c r="AS23" s="14"/>
-      <c r="AT23" s="14"/>
-      <c r="AU23" s="14"/>
-      <c r="AV23" s="8"/>
-      <c r="AW23" s="8"/>
-      <c r="AX23" s="8"/>
-      <c r="AY23" s="14"/>
-      <c r="AZ23" s="14"/>
-      <c r="BA23" s="14"/>
-      <c r="BB23" s="14"/>
-      <c r="BC23" s="8"/>
-      <c r="BD23" s="8"/>
-      <c r="BE23" s="8"/>
-      <c r="BF23" s="14"/>
-      <c r="BG23" s="14"/>
-      <c r="BH23" s="14"/>
-      <c r="BI23" s="14"/>
-      <c r="BJ23" s="8"/>
-      <c r="BK23" s="8"/>
-      <c r="BL23" s="8"/>
-      <c r="BM23" s="14"/>
-      <c r="BN23" s="14"/>
-      <c r="BO23" s="14"/>
-      <c r="BP23" s="8"/>
-      <c r="BQ23" s="8"/>
-      <c r="BR23" s="14"/>
-      <c r="BS23" s="14"/>
-      <c r="BT23" s="14"/>
-      <c r="BU23" s="8"/>
-      <c r="BV23" s="8"/>
-      <c r="BW23" s="14"/>
-      <c r="BX23" s="14"/>
-      <c r="BY23" s="14"/>
-      <c r="BZ23" s="8"/>
-      <c r="CA23" s="8"/>
-      <c r="CB23" s="14"/>
-      <c r="CC23" s="14"/>
-      <c r="CD23" s="14"/>
-      <c r="CE23" s="8"/>
-      <c r="CF23" s="8"/>
-      <c r="CG23" s="14"/>
-      <c r="CH23" s="14"/>
-      <c r="CI23" s="14"/>
-      <c r="CJ23" s="8"/>
-      <c r="CK23" s="8"/>
-      <c r="CL23" s="14"/>
-      <c r="CM23" s="14"/>
-      <c r="CN23" s="14"/>
-      <c r="CO23" s="14"/>
-      <c r="CP23" s="9"/>
-      <c r="CQ23" s="9"/>
-      <c r="CR23" s="14"/>
-      <c r="CS23" s="14"/>
-      <c r="CT23" s="14"/>
-      <c r="CU23" s="14"/>
-      <c r="CV23" s="8"/>
-      <c r="CW23" s="8"/>
-      <c r="CX23" s="14"/>
-      <c r="CY23" s="14"/>
-      <c r="CZ23" s="14"/>
-      <c r="DA23" s="14"/>
-      <c r="DB23" s="8"/>
-      <c r="DC23" s="8"/>
+      <c r="S23" s="14">
+        <v>0</v>
+      </c>
+      <c r="T23" s="14">
+        <v>0</v>
+      </c>
+      <c r="U23" s="8">
+        <v>0</v>
+      </c>
+      <c r="V23" s="8">
+        <v>0</v>
+      </c>
+      <c r="W23" s="14">
+        <v>0</v>
+      </c>
+      <c r="X23" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="AC23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="AD23" s="14">
+        <v>5</v>
+      </c>
+      <c r="AE23" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="14">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="AJ23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="AK23" s="14">
+        <v>5</v>
+      </c>
+      <c r="AL23" s="14">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="14">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="AQ23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="AR23" s="14">
+        <v>5</v>
+      </c>
+      <c r="AS23" s="14">
+        <v>0</v>
+      </c>
+      <c r="AT23" s="14">
+        <v>0</v>
+      </c>
+      <c r="AU23" s="14">
+        <v>0</v>
+      </c>
+      <c r="AV23" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="AX23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="AY23" s="14">
+        <v>5</v>
+      </c>
+      <c r="AZ23" s="14">
+        <v>0</v>
+      </c>
+      <c r="BA23" s="14">
+        <v>0</v>
+      </c>
+      <c r="BB23" s="14">
+        <v>0</v>
+      </c>
+      <c r="BC23" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="BE23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="BF23" s="14">
+        <v>5</v>
+      </c>
+      <c r="BG23" s="14">
+        <v>0</v>
+      </c>
+      <c r="BH23" s="14">
+        <v>0</v>
+      </c>
+      <c r="BI23" s="14">
+        <v>0</v>
+      </c>
+      <c r="BJ23" s="8">
+        <v>0</v>
+      </c>
+      <c r="BK23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="BL23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="BM23" s="14">
+        <v>5</v>
+      </c>
+      <c r="BN23" s="14">
+        <v>0</v>
+      </c>
+      <c r="BO23" s="14">
+        <v>0</v>
+      </c>
+      <c r="BP23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="BQ23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="BR23" s="14">
+        <v>5</v>
+      </c>
+      <c r="BS23" s="14">
+        <v>0</v>
+      </c>
+      <c r="BT23" s="14">
+        <v>0</v>
+      </c>
+      <c r="BU23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="BV23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="BW23" s="14">
+        <v>5</v>
+      </c>
+      <c r="BX23" s="14">
+        <v>0</v>
+      </c>
+      <c r="BY23" s="14">
+        <v>0</v>
+      </c>
+      <c r="BZ23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="CA23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="CB23" s="14">
+        <v>5</v>
+      </c>
+      <c r="CC23" s="14">
+        <v>0</v>
+      </c>
+      <c r="CD23" s="14">
+        <v>0</v>
+      </c>
+      <c r="CE23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="CF23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="CG23" s="14">
+        <v>5</v>
+      </c>
+      <c r="CH23" s="14">
+        <v>0</v>
+      </c>
+      <c r="CI23" s="14">
+        <v>0</v>
+      </c>
+      <c r="CJ23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="CK23" s="8">
+        <v>5000</v>
+      </c>
+      <c r="CL23" s="14">
+        <v>5</v>
+      </c>
+      <c r="CM23" s="14">
+        <v>0</v>
+      </c>
+      <c r="CN23" s="14">
+        <v>0</v>
+      </c>
+      <c r="CO23" s="14">
+        <v>0</v>
+      </c>
+      <c r="CP23" s="9">
+        <v>55000</v>
+      </c>
+      <c r="CQ23" s="9">
+        <v>55000</v>
+      </c>
+      <c r="CR23" s="14">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="CS23" s="14">
+        <v>0</v>
+      </c>
+      <c r="CT23" s="14">
+        <v>0</v>
+      </c>
+      <c r="CU23" s="14">
+        <v>0</v>
+      </c>
+      <c r="CV23" s="8">
+        <v>-55000</v>
+      </c>
+      <c r="CW23" s="8">
+        <v>-55000</v>
+      </c>
+      <c r="CX23" s="14">
+        <v>0</v>
+      </c>
+      <c r="CY23" s="14">
+        <v>0</v>
+      </c>
+      <c r="CZ23" s="14">
+        <v>0</v>
+      </c>
+      <c r="DA23" s="14">
+        <v>0</v>
+      </c>
+      <c r="DB23" s="8">
+        <v>55000</v>
+      </c>
+      <c r="DC23" s="8">
+        <v>55000</v>
+      </c>
     </row>
     <row r="24" spans="1:107" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
@@ -8111,38 +8116,38 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>107</v>
       </c>
       <c r="E24" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>170</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I24" s="5">
-        <v>5842263202</v>
+        <v>5841813202</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>110</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>114</v>
@@ -8178,13 +8183,13 @@
         <v>0</v>
       </c>
       <c r="AB24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AC24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AD24" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE24" s="8">
         <v>0</v>
@@ -8199,13 +8204,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AJ24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL24" s="8">
         <v>0</v>
@@ -8220,13 +8225,13 @@
         <v>0</v>
       </c>
       <c r="AP24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AQ24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AR24" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AS24" s="8">
         <v>0</v>
@@ -8241,13 +8246,13 @@
         <v>0</v>
       </c>
       <c r="AW24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AX24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AY24" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AZ24" s="8">
         <v>0</v>
@@ -8262,13 +8267,13 @@
         <v>0</v>
       </c>
       <c r="BD24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="BE24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="BF24" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BG24" s="8">
         <v>0</v>
@@ -8283,13 +8288,13 @@
         <v>0</v>
       </c>
       <c r="BK24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="BL24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="BM24" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BN24" s="8">
         <v>0</v>
@@ -8298,13 +8303,13 @@
         <v>0</v>
       </c>
       <c r="BP24" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="BQ24" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="BR24" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BS24" s="8">
         <v>0</v>
@@ -8313,13 +8318,13 @@
         <v>0</v>
       </c>
       <c r="BU24" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="BV24" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="BW24" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BX24" s="8">
         <v>0</v>
@@ -8328,13 +8333,13 @@
         <v>0</v>
       </c>
       <c r="BZ24" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="CA24" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="CB24" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CC24" s="8">
         <v>0</v>
@@ -8343,13 +8348,13 @@
         <v>0</v>
       </c>
       <c r="CE24" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="CF24" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="CG24" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CH24" s="8">
         <v>0</v>
@@ -8358,13 +8363,13 @@
         <v>0</v>
       </c>
       <c r="CJ24" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="CK24" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="CL24" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM24" s="8">
         <v>0</v>
@@ -8376,13 +8381,13 @@
         <v>0</v>
       </c>
       <c r="CP24" s="9">
-        <v>55000</v>
+        <v>20000</v>
       </c>
       <c r="CQ24" s="9">
-        <v>55000</v>
+        <v>20000</v>
       </c>
       <c r="CR24" s="8">
-        <v>4.5999999999999996</v>
+        <v>2</v>
       </c>
       <c r="CS24" s="8">
         <v>0</v>
@@ -8394,10 +8399,10 @@
         <v>0</v>
       </c>
       <c r="CV24" s="8">
-        <v>-55000</v>
+        <v>-20000</v>
       </c>
       <c r="CW24" s="8">
-        <v>-55000</v>
+        <v>-20000</v>
       </c>
       <c r="CX24" s="8">
         <v>0</v>
@@ -8412,10 +8417,10 @@
         <v>0</v>
       </c>
       <c r="DB24" s="8">
-        <v>55000</v>
+        <v>20000</v>
       </c>
       <c r="DC24" s="8">
-        <v>55000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="25" spans="1:107" x14ac:dyDescent="0.3">
@@ -8424,38 +8429,38 @@
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>107</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G25" s="11"/>
       <c r="H25" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I25" s="11">
-        <v>5841813202</v>
+        <v>5842263202</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>110</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="O25" s="12" t="s">
         <v>114</v>
@@ -8491,13 +8496,13 @@
         <v>0</v>
       </c>
       <c r="AB25" s="8">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AC25" s="8">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AD25" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE25" s="14">
         <v>0</v>
@@ -8512,13 +8517,13 @@
         <v>0</v>
       </c>
       <c r="AI25" s="8">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AJ25" s="8">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AK25" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL25" s="14">
         <v>0</v>
@@ -8533,13 +8538,13 @@
         <v>0</v>
       </c>
       <c r="AP25" s="8">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AQ25" s="8">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AR25" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AS25" s="14">
         <v>0</v>
@@ -8554,13 +8559,13 @@
         <v>0</v>
       </c>
       <c r="AW25" s="8">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AX25" s="8">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AY25" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AZ25" s="14">
         <v>0</v>
@@ -8575,13 +8580,13 @@
         <v>0</v>
       </c>
       <c r="BD25" s="8">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="BE25" s="8">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="BF25" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BG25" s="14">
         <v>0</v>
@@ -8596,13 +8601,13 @@
         <v>0</v>
       </c>
       <c r="BK25" s="8">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="BL25" s="8">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="BM25" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BN25" s="14">
         <v>0</v>
@@ -8611,13 +8616,13 @@
         <v>0</v>
       </c>
       <c r="BP25" s="8">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="BQ25" s="8">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="BR25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BS25" s="14">
         <v>0</v>
@@ -8626,13 +8631,13 @@
         <v>0</v>
       </c>
       <c r="BU25" s="8">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="BV25" s="8">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="BW25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BX25" s="14">
         <v>0</v>
@@ -8641,13 +8646,13 @@
         <v>0</v>
       </c>
       <c r="BZ25" s="8">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="CA25" s="8">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="CB25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CC25" s="14">
         <v>0</v>
@@ -8656,13 +8661,13 @@
         <v>0</v>
       </c>
       <c r="CE25" s="8">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="CF25" s="8">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="CG25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CH25" s="14">
         <v>0</v>
@@ -8671,13 +8676,13 @@
         <v>0</v>
       </c>
       <c r="CJ25" s="8">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="CK25" s="8">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="CL25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM25" s="14">
         <v>0</v>
@@ -8689,13 +8694,13 @@
         <v>0</v>
       </c>
       <c r="CP25" s="9">
-        <v>20000</v>
+        <v>55000</v>
       </c>
       <c r="CQ25" s="9">
-        <v>20000</v>
+        <v>55000</v>
       </c>
       <c r="CR25" s="14">
-        <v>2</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="CS25" s="14">
         <v>0</v>
@@ -8707,10 +8712,10 @@
         <v>0</v>
       </c>
       <c r="CV25" s="8">
-        <v>-20000</v>
+        <v>-55000</v>
       </c>
       <c r="CW25" s="8">
-        <v>-20000</v>
+        <v>-55000</v>
       </c>
       <c r="CX25" s="14">
         <v>0</v>
@@ -8725,10 +8730,10 @@
         <v>0</v>
       </c>
       <c r="DB25" s="8">
-        <v>20000</v>
+        <v>55000</v>
       </c>
       <c r="DC25" s="8">
-        <v>20000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="26" spans="1:107" x14ac:dyDescent="0.3">
@@ -8737,38 +8742,38 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>107</v>
       </c>
       <c r="E26" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>170</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I26" s="5">
-        <v>5842263202</v>
+        <v>5841813202</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>110</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>114</v>
@@ -8804,13 +8809,13 @@
         <v>0</v>
       </c>
       <c r="AB26" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AC26" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AD26" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE26" s="8">
         <v>0</v>
@@ -8825,13 +8830,13 @@
         <v>0</v>
       </c>
       <c r="AI26" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AJ26" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL26" s="8">
         <v>0</v>
@@ -8846,13 +8851,13 @@
         <v>0</v>
       </c>
       <c r="AP26" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AQ26" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AR26" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AS26" s="8">
         <v>0</v>
@@ -8867,13 +8872,13 @@
         <v>0</v>
       </c>
       <c r="AW26" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AX26" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AY26" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AZ26" s="8">
         <v>0</v>
@@ -8888,13 +8893,13 @@
         <v>0</v>
       </c>
       <c r="BD26" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="BE26" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="BF26" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BG26" s="8">
         <v>0</v>
@@ -8909,13 +8914,13 @@
         <v>0</v>
       </c>
       <c r="BK26" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="BL26" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="BM26" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BN26" s="8">
         <v>0</v>
@@ -8924,13 +8929,13 @@
         <v>0</v>
       </c>
       <c r="BP26" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="BQ26" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="BR26" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BS26" s="8">
         <v>0</v>
@@ -8939,13 +8944,13 @@
         <v>0</v>
       </c>
       <c r="BU26" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="BV26" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="BW26" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BX26" s="8">
         <v>0</v>
@@ -8954,13 +8959,13 @@
         <v>0</v>
       </c>
       <c r="BZ26" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="CA26" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="CB26" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CC26" s="8">
         <v>0</v>
@@ -8969,13 +8974,13 @@
         <v>0</v>
       </c>
       <c r="CE26" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="CF26" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="CG26" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CH26" s="8">
         <v>0</v>
@@ -8984,13 +8989,13 @@
         <v>0</v>
       </c>
       <c r="CJ26" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="CK26" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="CL26" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM26" s="8">
         <v>0</v>
@@ -9002,13 +9007,13 @@
         <v>0</v>
       </c>
       <c r="CP26" s="9">
-        <v>55000</v>
+        <v>20000</v>
       </c>
       <c r="CQ26" s="9">
-        <v>55000</v>
+        <v>20000</v>
       </c>
       <c r="CR26" s="8">
-        <v>4.5999999999999996</v>
+        <v>2</v>
       </c>
       <c r="CS26" s="8">
         <v>0</v>
@@ -9020,10 +9025,10 @@
         <v>0</v>
       </c>
       <c r="CV26" s="8">
-        <v>-55000</v>
+        <v>-20000</v>
       </c>
       <c r="CW26" s="8">
-        <v>-55000</v>
+        <v>-20000</v>
       </c>
       <c r="CX26" s="8">
         <v>0</v>
@@ -9038,332 +9043,395 @@
         <v>0</v>
       </c>
       <c r="DB26" s="8">
-        <v>55000</v>
+        <v>20000</v>
       </c>
       <c r="DC26" s="8">
-        <v>55000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="27" spans="1:107" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
-        <v>127</v>
-      </c>
+      <c r="A27" s="10"/>
       <c r="B27" s="10"/>
-      <c r="C27" s="11" t="s">
-        <v>168</v>
-      </c>
+      <c r="C27" s="11"/>
       <c r="D27" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>172</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
       <c r="G27" s="11"/>
-      <c r="H27" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="I27" s="11">
-        <v>5841813202</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="K27" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="L27" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="N27" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="O27" s="12" t="s">
-        <v>114</v>
-      </c>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="12"/>
       <c r="P27" s="12"/>
       <c r="Q27" s="13"/>
       <c r="R27" s="13"/>
       <c r="S27" s="14">
+        <f>SUM($S$23:$S$26)</f>
         <v>0</v>
       </c>
       <c r="T27" s="14">
+        <f>SUM($T$23:$T$26)</f>
         <v>0</v>
       </c>
       <c r="U27" s="8">
+        <f>SUM($U$23:$U$26)</f>
         <v>0</v>
       </c>
       <c r="V27" s="8">
+        <f>SUM($V$23:$V$26)</f>
         <v>0</v>
       </c>
       <c r="W27" s="14">
+        <f>SUM($W$23:$W$26)</f>
         <v>0</v>
       </c>
       <c r="X27" s="14">
+        <f>SUM($X$23:$X$26)</f>
         <v>0</v>
       </c>
       <c r="Y27" s="14">
+        <f>SUM($Y$23:$Y$26)</f>
         <v>0</v>
       </c>
       <c r="Z27" s="14">
+        <f>SUM($Z$23:$Z$26)</f>
         <v>0</v>
       </c>
       <c r="AA27" s="14">
+        <f>SUM($AA$23:$AA$26)</f>
         <v>0</v>
       </c>
       <c r="AB27" s="8">
-        <v>0</v>
+        <f>SUM($AB$23:$AB$26)</f>
+        <v>10000</v>
       </c>
       <c r="AC27" s="8">
-        <v>0</v>
+        <f>SUM($AC$23:$AC$26)</f>
+        <v>10000</v>
       </c>
       <c r="AD27" s="14">
-        <v>0</v>
+        <f>SUM($AD$23:$AD$26)</f>
+        <v>10</v>
       </c>
       <c r="AE27" s="14">
+        <f>SUM($AE$23:$AE$26)</f>
         <v>0</v>
       </c>
       <c r="AF27" s="14">
+        <f>SUM($AF$23:$AF$26)</f>
         <v>0</v>
       </c>
       <c r="AG27" s="14">
+        <f>SUM($AG$23:$AG$26)</f>
         <v>0</v>
       </c>
       <c r="AH27" s="8">
+        <f>SUM($AH$23:$AH$26)</f>
         <v>0</v>
       </c>
       <c r="AI27" s="8">
-        <v>0</v>
+        <f>SUM($AI$23:$AI$26)</f>
+        <v>10000</v>
       </c>
       <c r="AJ27" s="8">
-        <v>0</v>
+        <f>SUM($AJ$23:$AJ$26)</f>
+        <v>10000</v>
       </c>
       <c r="AK27" s="14">
-        <v>0</v>
+        <f>SUM($AK$23:$AK$26)</f>
+        <v>10</v>
       </c>
       <c r="AL27" s="14">
+        <f>SUM($AL$23:$AL$26)</f>
         <v>0</v>
       </c>
       <c r="AM27" s="14">
+        <f>SUM($AM$23:$AM$26)</f>
         <v>0</v>
       </c>
       <c r="AN27" s="14">
+        <f>SUM($AN$23:$AN$26)</f>
         <v>0</v>
       </c>
       <c r="AO27" s="8">
+        <f>SUM($AO$23:$AO$26)</f>
         <v>0</v>
       </c>
       <c r="AP27" s="8">
-        <v>0</v>
+        <f>SUM($AP$23:$AP$26)</f>
+        <v>10000</v>
       </c>
       <c r="AQ27" s="8">
-        <v>0</v>
+        <f>SUM($AQ$23:$AQ$26)</f>
+        <v>10000</v>
       </c>
       <c r="AR27" s="14">
-        <v>0</v>
+        <f>SUM($AR$23:$AR$26)</f>
+        <v>10</v>
       </c>
       <c r="AS27" s="14">
+        <f>SUM($AS$23:$AS$26)</f>
         <v>0</v>
       </c>
       <c r="AT27" s="14">
+        <f>SUM($AT$23:$AT$26)</f>
         <v>0</v>
       </c>
       <c r="AU27" s="14">
+        <f>SUM($AU$23:$AU$26)</f>
         <v>0</v>
       </c>
       <c r="AV27" s="8">
+        <f>SUM($AV$23:$AV$26)</f>
         <v>0</v>
       </c>
       <c r="AW27" s="8">
-        <v>0</v>
+        <f>SUM($AW$23:$AW$26)</f>
+        <v>10000</v>
       </c>
       <c r="AX27" s="8">
-        <v>0</v>
+        <f>SUM($AX$23:$AX$26)</f>
+        <v>10000</v>
       </c>
       <c r="AY27" s="14">
-        <v>0</v>
+        <f>SUM($AY$23:$AY$26)</f>
+        <v>10</v>
       </c>
       <c r="AZ27" s="14">
+        <f>SUM($AZ$23:$AZ$26)</f>
         <v>0</v>
       </c>
       <c r="BA27" s="14">
+        <f>SUM($BA$23:$BA$26)</f>
         <v>0</v>
       </c>
       <c r="BB27" s="14">
+        <f>SUM($BB$23:$BB$26)</f>
         <v>0</v>
       </c>
       <c r="BC27" s="8">
+        <f>SUM($BC$23:$BC$26)</f>
         <v>0</v>
       </c>
       <c r="BD27" s="8">
-        <v>0</v>
+        <f>SUM($BD$23:$BD$26)</f>
+        <v>10000</v>
       </c>
       <c r="BE27" s="8">
-        <v>0</v>
+        <f>SUM($BE$23:$BE$26)</f>
+        <v>10000</v>
       </c>
       <c r="BF27" s="14">
-        <v>0</v>
+        <f>SUM($BF$23:$BF$26)</f>
+        <v>10</v>
       </c>
       <c r="BG27" s="14">
+        <f>SUM($BG$23:$BG$26)</f>
         <v>0</v>
       </c>
       <c r="BH27" s="14">
+        <f>SUM($BH$23:$BH$26)</f>
         <v>0</v>
       </c>
       <c r="BI27" s="14">
+        <f>SUM($BI$23:$BI$26)</f>
         <v>0</v>
       </c>
       <c r="BJ27" s="8">
+        <f>SUM($BJ$23:$BJ$26)</f>
         <v>0</v>
       </c>
       <c r="BK27" s="8">
-        <v>0</v>
+        <f>SUM($BK$23:$BK$26)</f>
+        <v>10000</v>
       </c>
       <c r="BL27" s="8">
-        <v>0</v>
+        <f>SUM($BL$23:$BL$26)</f>
+        <v>10000</v>
       </c>
       <c r="BM27" s="14">
-        <v>0</v>
+        <f>SUM($BM$23:$BM$26)</f>
+        <v>10</v>
       </c>
       <c r="BN27" s="14">
+        <f>SUM($BN$23:$BN$26)</f>
         <v>0</v>
       </c>
       <c r="BO27" s="14">
+        <f>SUM($BO$23:$BO$26)</f>
         <v>0</v>
       </c>
       <c r="BP27" s="8">
-        <v>4000</v>
+        <f>SUM($BP$23:$BP$26)</f>
+        <v>18000</v>
       </c>
       <c r="BQ27" s="8">
-        <v>4000</v>
+        <f>SUM($BQ$23:$BQ$26)</f>
+        <v>18000</v>
       </c>
       <c r="BR27" s="14">
-        <v>4</v>
+        <f>SUM($BR$23:$BR$26)</f>
+        <v>18</v>
       </c>
       <c r="BS27" s="14">
+        <f>SUM($BS$23:$BS$26)</f>
         <v>0</v>
       </c>
       <c r="BT27" s="14">
+        <f>SUM($BT$23:$BT$26)</f>
         <v>0</v>
       </c>
       <c r="BU27" s="8">
-        <v>4000</v>
+        <f>SUM($BU$23:$BU$26)</f>
+        <v>18000</v>
       </c>
       <c r="BV27" s="8">
-        <v>4000</v>
+        <f>SUM($BV$23:$BV$26)</f>
+        <v>18000</v>
       </c>
       <c r="BW27" s="14">
-        <v>4</v>
+        <f>SUM($BW$23:$BW$26)</f>
+        <v>18</v>
       </c>
       <c r="BX27" s="14">
+        <f>SUM($BX$23:$BX$26)</f>
         <v>0</v>
       </c>
       <c r="BY27" s="14">
+        <f>SUM($BY$23:$BY$26)</f>
         <v>0</v>
       </c>
       <c r="BZ27" s="8">
-        <v>4000</v>
+        <f>SUM($BZ$23:$BZ$26)</f>
+        <v>18000</v>
       </c>
       <c r="CA27" s="8">
-        <v>4000</v>
+        <f>SUM($CA$23:$CA$26)</f>
+        <v>18000</v>
       </c>
       <c r="CB27" s="14">
-        <v>4</v>
+        <f>SUM($CB$23:$CB$26)</f>
+        <v>18</v>
       </c>
       <c r="CC27" s="14">
+        <f>SUM($CC$23:$CC$26)</f>
         <v>0</v>
       </c>
       <c r="CD27" s="14">
+        <f>SUM($CD$23:$CD$26)</f>
         <v>0</v>
       </c>
       <c r="CE27" s="8">
-        <v>4000</v>
+        <f>SUM($CE$23:$CE$26)</f>
+        <v>18000</v>
       </c>
       <c r="CF27" s="8">
-        <v>4000</v>
+        <f>SUM($CF$23:$CF$26)</f>
+        <v>18000</v>
       </c>
       <c r="CG27" s="14">
-        <v>4</v>
+        <f>SUM($CG$23:$CG$26)</f>
+        <v>18</v>
       </c>
       <c r="CH27" s="14">
+        <f>SUM($CH$23:$CH$26)</f>
         <v>0</v>
       </c>
       <c r="CI27" s="14">
+        <f>SUM($CI$23:$CI$26)</f>
         <v>0</v>
       </c>
       <c r="CJ27" s="8">
-        <v>4000</v>
+        <f>SUM($CJ$23:$CJ$26)</f>
+        <v>18000</v>
       </c>
       <c r="CK27" s="8">
-        <v>4000</v>
+        <f>SUM($CK$23:$CK$26)</f>
+        <v>18000</v>
       </c>
       <c r="CL27" s="14">
-        <v>4</v>
+        <f>SUM($CL$23:$CL$26)</f>
+        <v>18</v>
       </c>
       <c r="CM27" s="14">
+        <f>SUM($CM$23:$CM$26)</f>
         <v>0</v>
       </c>
       <c r="CN27" s="14">
+        <f>SUM($CN$23:$CN$26)</f>
         <v>0</v>
       </c>
       <c r="CO27" s="14">
+        <f>SUM($CO$23:$CO$26)</f>
         <v>0</v>
       </c>
       <c r="CP27" s="9">
-        <v>20000</v>
+        <f>SUM($CP$23:$CP$26)</f>
+        <v>150000</v>
       </c>
       <c r="CQ27" s="9">
-        <v>20000</v>
+        <f>SUM($CQ$23:$CQ$26)</f>
+        <v>150000</v>
       </c>
       <c r="CR27" s="14">
-        <v>2</v>
+        <f>SUM($CR$23:$CR$26)</f>
+        <v>13.2</v>
       </c>
       <c r="CS27" s="14">
+        <f>SUM($CS$23:$CS$26)</f>
         <v>0</v>
       </c>
       <c r="CT27" s="14">
+        <f>SUM($CT$23:$CT$26)</f>
         <v>0</v>
       </c>
       <c r="CU27" s="14">
+        <f>SUM($CU$23:$CU$26)</f>
         <v>0</v>
       </c>
       <c r="CV27" s="8">
-        <v>-20000</v>
+        <f>SUM($CV$23:$CV$26)</f>
+        <v>-150000</v>
       </c>
       <c r="CW27" s="8">
-        <v>-20000</v>
+        <f>SUM($CW$23:$CW$26)</f>
+        <v>-150000</v>
       </c>
       <c r="CX27" s="14">
+        <f>SUM($CX$23:$CX$26)</f>
         <v>0</v>
       </c>
       <c r="CY27" s="14">
+        <f>SUM($CY$23:$CY$26)</f>
         <v>0</v>
       </c>
       <c r="CZ27" s="14">
+        <f>SUM($CZ$23:$CZ$26)</f>
         <v>0</v>
       </c>
       <c r="DA27" s="14">
+        <f>SUM($DA$23:$DA$26)</f>
         <v>0</v>
       </c>
       <c r="DB27" s="8">
-        <v>20000</v>
+        <f>SUM($DB$23:$DB$26)</f>
+        <v>150000</v>
       </c>
       <c r="DC27" s="8">
-        <v>20000</v>
+        <f>SUM($DC$23:$DC$26)</f>
+        <v>150000</v>
       </c>
     </row>
     <row r="28" spans="1:107" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="5" t="s">
-        <v>174</v>
-      </c>
+      <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -9378,471 +9446,408 @@
       <c r="P28" s="6"/>
       <c r="Q28" s="7"/>
       <c r="R28" s="7"/>
-      <c r="S28" s="8">
-        <f>SUM($S$24:$S$27)</f>
-        <v>0</v>
-      </c>
-      <c r="T28" s="8">
-        <f>SUM($T$24:$T$27)</f>
-        <v>0</v>
-      </c>
-      <c r="U28" s="8">
-        <f>SUM($U$24:$U$27)</f>
-        <v>0</v>
-      </c>
-      <c r="V28" s="8">
-        <f>SUM($V$24:$V$27)</f>
-        <v>0</v>
-      </c>
-      <c r="W28" s="8">
-        <f>SUM($W$24:$W$27)</f>
-        <v>0</v>
-      </c>
-      <c r="X28" s="8">
-        <f>SUM($X$24:$X$27)</f>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="8">
-        <f>SUM($Y$24:$Y$27)</f>
-        <v>0</v>
-      </c>
-      <c r="Z28" s="8">
-        <f>SUM($Z$24:$Z$27)</f>
-        <v>0</v>
-      </c>
-      <c r="AA28" s="8">
-        <f>SUM($AA$24:$AA$27)</f>
-        <v>0</v>
-      </c>
-      <c r="AB28" s="8">
-        <f>SUM($AB$24:$AB$27)</f>
-        <v>10000</v>
-      </c>
-      <c r="AC28" s="8">
-        <f>SUM($AC$24:$AC$27)</f>
-        <v>10000</v>
-      </c>
-      <c r="AD28" s="8">
-        <f>SUM($AD$24:$AD$27)</f>
-        <v>10</v>
-      </c>
-      <c r="AE28" s="8">
-        <f>SUM($AE$24:$AE$27)</f>
-        <v>0</v>
-      </c>
-      <c r="AF28" s="8">
-        <f>SUM($AF$24:$AF$27)</f>
-        <v>0</v>
-      </c>
-      <c r="AG28" s="8">
-        <f>SUM($AG$24:$AG$27)</f>
-        <v>0</v>
-      </c>
-      <c r="AH28" s="8">
-        <f>SUM($AH$24:$AH$27)</f>
-        <v>0</v>
-      </c>
-      <c r="AI28" s="8">
-        <f>SUM($AI$24:$AI$27)</f>
-        <v>10000</v>
-      </c>
-      <c r="AJ28" s="8">
-        <f>SUM($AJ$24:$AJ$27)</f>
-        <v>10000</v>
-      </c>
-      <c r="AK28" s="8">
-        <f>SUM($AK$24:$AK$27)</f>
-        <v>10</v>
-      </c>
-      <c r="AL28" s="8">
-        <f>SUM($AL$24:$AL$27)</f>
-        <v>0</v>
-      </c>
-      <c r="AM28" s="8">
-        <f>SUM($AM$24:$AM$27)</f>
-        <v>0</v>
-      </c>
-      <c r="AN28" s="8">
-        <f>SUM($AN$24:$AN$27)</f>
-        <v>0</v>
-      </c>
-      <c r="AO28" s="8">
-        <f>SUM($AO$24:$AO$27)</f>
-        <v>0</v>
-      </c>
-      <c r="AP28" s="8">
-        <f>SUM($AP$24:$AP$27)</f>
-        <v>10000</v>
-      </c>
-      <c r="AQ28" s="8">
-        <f>SUM($AQ$24:$AQ$27)</f>
-        <v>10000</v>
-      </c>
-      <c r="AR28" s="8">
-        <f>SUM($AR$24:$AR$27)</f>
-        <v>10</v>
-      </c>
-      <c r="AS28" s="8">
-        <f>SUM($AS$24:$AS$27)</f>
-        <v>0</v>
-      </c>
-      <c r="AT28" s="8">
-        <f>SUM($AT$24:$AT$27)</f>
-        <v>0</v>
-      </c>
-      <c r="AU28" s="8">
-        <f>SUM($AU$24:$AU$27)</f>
-        <v>0</v>
-      </c>
-      <c r="AV28" s="8">
-        <f>SUM($AV$24:$AV$27)</f>
-        <v>0</v>
-      </c>
-      <c r="AW28" s="8">
-        <f>SUM($AW$24:$AW$27)</f>
-        <v>10000</v>
-      </c>
-      <c r="AX28" s="8">
-        <f>SUM($AX$24:$AX$27)</f>
-        <v>10000</v>
-      </c>
-      <c r="AY28" s="8">
-        <f>SUM($AY$24:$AY$27)</f>
-        <v>10</v>
-      </c>
-      <c r="AZ28" s="8">
-        <f>SUM($AZ$24:$AZ$27)</f>
-        <v>0</v>
-      </c>
-      <c r="BA28" s="8">
-        <f>SUM($BA$24:$BA$27)</f>
-        <v>0</v>
-      </c>
-      <c r="BB28" s="8">
-        <f>SUM($BB$24:$BB$27)</f>
-        <v>0</v>
-      </c>
-      <c r="BC28" s="8">
-        <f>SUM($BC$24:$BC$27)</f>
-        <v>0</v>
-      </c>
-      <c r="BD28" s="8">
-        <f>SUM($BD$24:$BD$27)</f>
-        <v>10000</v>
-      </c>
-      <c r="BE28" s="8">
-        <f>SUM($BE$24:$BE$27)</f>
-        <v>10000</v>
-      </c>
-      <c r="BF28" s="8">
-        <f>SUM($BF$24:$BF$27)</f>
-        <v>10</v>
-      </c>
-      <c r="BG28" s="8">
-        <f>SUM($BG$24:$BG$27)</f>
-        <v>0</v>
-      </c>
-      <c r="BH28" s="8">
-        <f>SUM($BH$24:$BH$27)</f>
-        <v>0</v>
-      </c>
-      <c r="BI28" s="8">
-        <f>SUM($BI$24:$BI$27)</f>
-        <v>0</v>
-      </c>
-      <c r="BJ28" s="8">
-        <f>SUM($BJ$24:$BJ$27)</f>
-        <v>0</v>
-      </c>
-      <c r="BK28" s="8">
-        <f>SUM($BK$24:$BK$27)</f>
-        <v>10000</v>
-      </c>
-      <c r="BL28" s="8">
-        <f>SUM($BL$24:$BL$27)</f>
-        <v>10000</v>
-      </c>
-      <c r="BM28" s="8">
-        <f>SUM($BM$24:$BM$27)</f>
-        <v>10</v>
-      </c>
-      <c r="BN28" s="8">
-        <f>SUM($BN$24:$BN$27)</f>
-        <v>0</v>
-      </c>
-      <c r="BO28" s="8">
-        <f>SUM($BO$24:$BO$27)</f>
-        <v>0</v>
-      </c>
-      <c r="BP28" s="8">
-        <f>SUM($BP$24:$BP$27)</f>
-        <v>18000</v>
-      </c>
-      <c r="BQ28" s="8">
-        <f>SUM($BQ$24:$BQ$27)</f>
-        <v>18000</v>
-      </c>
-      <c r="BR28" s="8">
-        <f>SUM($BR$24:$BR$27)</f>
-        <v>18</v>
-      </c>
-      <c r="BS28" s="8">
-        <f>SUM($BS$24:$BS$27)</f>
-        <v>0</v>
-      </c>
-      <c r="BT28" s="8">
-        <f>SUM($BT$24:$BT$27)</f>
-        <v>0</v>
-      </c>
-      <c r="BU28" s="8">
-        <f>SUM($BU$24:$BU$27)</f>
-        <v>18000</v>
-      </c>
-      <c r="BV28" s="8">
-        <f>SUM($BV$24:$BV$27)</f>
-        <v>18000</v>
-      </c>
-      <c r="BW28" s="8">
-        <f>SUM($BW$24:$BW$27)</f>
-        <v>18</v>
-      </c>
-      <c r="BX28" s="8">
-        <f>SUM($BX$24:$BX$27)</f>
-        <v>0</v>
-      </c>
-      <c r="BY28" s="8">
-        <f>SUM($BY$24:$BY$27)</f>
-        <v>0</v>
-      </c>
-      <c r="BZ28" s="8">
-        <f>SUM($BZ$24:$BZ$27)</f>
-        <v>18000</v>
-      </c>
-      <c r="CA28" s="8">
-        <f>SUM($CA$24:$CA$27)</f>
-        <v>18000</v>
-      </c>
-      <c r="CB28" s="8">
-        <f>SUM($CB$24:$CB$27)</f>
-        <v>18</v>
-      </c>
-      <c r="CC28" s="8">
-        <f>SUM($CC$24:$CC$27)</f>
-        <v>0</v>
-      </c>
-      <c r="CD28" s="8">
-        <f>SUM($CD$24:$CD$27)</f>
-        <v>0</v>
-      </c>
-      <c r="CE28" s="8">
-        <f>SUM($CE$24:$CE$27)</f>
-        <v>18000</v>
-      </c>
-      <c r="CF28" s="8">
-        <f>SUM($CF$24:$CF$27)</f>
-        <v>18000</v>
-      </c>
-      <c r="CG28" s="8">
-        <f>SUM($CG$24:$CG$27)</f>
-        <v>18</v>
-      </c>
-      <c r="CH28" s="8">
-        <f>SUM($CH$24:$CH$27)</f>
-        <v>0</v>
-      </c>
-      <c r="CI28" s="8">
-        <f>SUM($CI$24:$CI$27)</f>
-        <v>0</v>
-      </c>
-      <c r="CJ28" s="8">
-        <f>SUM($CJ$24:$CJ$27)</f>
-        <v>18000</v>
-      </c>
-      <c r="CK28" s="8">
-        <f>SUM($CK$24:$CK$27)</f>
-        <v>18000</v>
-      </c>
-      <c r="CL28" s="8">
-        <f>SUM($CL$24:$CL$27)</f>
-        <v>18</v>
-      </c>
-      <c r="CM28" s="8">
-        <f>SUM($CM$24:$CM$27)</f>
-        <v>0</v>
-      </c>
-      <c r="CN28" s="8">
-        <f>SUM($CN$24:$CN$27)</f>
-        <v>0</v>
-      </c>
-      <c r="CO28" s="8">
-        <f>SUM($CO$24:$CO$27)</f>
-        <v>0</v>
-      </c>
-      <c r="CP28" s="9">
-        <f>SUM($CP$24:$CP$27)</f>
-        <v>150000</v>
-      </c>
-      <c r="CQ28" s="9">
-        <f>SUM($CQ$24:$CQ$27)</f>
-        <v>150000</v>
-      </c>
-      <c r="CR28" s="8">
-        <f>SUM($CR$24:$CR$27)</f>
-        <v>13.2</v>
-      </c>
-      <c r="CS28" s="8">
-        <f>SUM($CS$24:$CS$27)</f>
-        <v>0</v>
-      </c>
-      <c r="CT28" s="8">
-        <f>SUM($CT$24:$CT$27)</f>
-        <v>0</v>
-      </c>
-      <c r="CU28" s="8">
-        <f>SUM($CU$24:$CU$27)</f>
-        <v>0</v>
-      </c>
-      <c r="CV28" s="8">
-        <f>SUM($CV$24:$CV$27)</f>
-        <v>-150000</v>
-      </c>
-      <c r="CW28" s="8">
-        <f>SUM($CW$24:$CW$27)</f>
-        <v>-150000</v>
-      </c>
-      <c r="CX28" s="8">
-        <f>SUM($CX$24:$CX$27)</f>
-        <v>0</v>
-      </c>
-      <c r="CY28" s="8">
-        <f>SUM($CY$24:$CY$27)</f>
-        <v>0</v>
-      </c>
-      <c r="CZ28" s="8">
-        <f>SUM($CZ$24:$CZ$27)</f>
-        <v>0</v>
-      </c>
-      <c r="DA28" s="8">
-        <f>SUM($DA$24:$DA$27)</f>
-        <v>0</v>
-      </c>
-      <c r="DB28" s="8">
-        <f>SUM($DB$24:$DB$27)</f>
-        <v>150000</v>
-      </c>
-      <c r="DC28" s="8">
-        <f>SUM($DC$24:$DC$27)</f>
-        <v>150000</v>
-      </c>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8"/>
+      <c r="V28" s="8"/>
+      <c r="W28" s="8"/>
+      <c r="X28" s="8"/>
+      <c r="Y28" s="8"/>
+      <c r="Z28" s="8"/>
+      <c r="AA28" s="8"/>
+      <c r="AB28" s="8"/>
+      <c r="AC28" s="8"/>
+      <c r="AD28" s="8"/>
+      <c r="AE28" s="8"/>
+      <c r="AF28" s="8"/>
+      <c r="AG28" s="8"/>
+      <c r="AH28" s="8"/>
+      <c r="AI28" s="8"/>
+      <c r="AJ28" s="8"/>
+      <c r="AK28" s="8"/>
+      <c r="AL28" s="8"/>
+      <c r="AM28" s="8"/>
+      <c r="AN28" s="8"/>
+      <c r="AO28" s="8"/>
+      <c r="AP28" s="8"/>
+      <c r="AQ28" s="8"/>
+      <c r="AR28" s="8"/>
+      <c r="AS28" s="8"/>
+      <c r="AT28" s="8"/>
+      <c r="AU28" s="8"/>
+      <c r="AV28" s="8"/>
+      <c r="AW28" s="8"/>
+      <c r="AX28" s="8"/>
+      <c r="AY28" s="8"/>
+      <c r="AZ28" s="8"/>
+      <c r="BA28" s="8"/>
+      <c r="BB28" s="8"/>
+      <c r="BC28" s="8"/>
+      <c r="BD28" s="8"/>
+      <c r="BE28" s="8"/>
+      <c r="BF28" s="8"/>
+      <c r="BG28" s="8"/>
+      <c r="BH28" s="8"/>
+      <c r="BI28" s="8"/>
+      <c r="BJ28" s="8"/>
+      <c r="BK28" s="8"/>
+      <c r="BL28" s="8"/>
+      <c r="BM28" s="8"/>
+      <c r="BN28" s="8"/>
+      <c r="BO28" s="8"/>
+      <c r="BP28" s="8"/>
+      <c r="BQ28" s="8"/>
+      <c r="BR28" s="8"/>
+      <c r="BS28" s="8"/>
+      <c r="BT28" s="8"/>
+      <c r="BU28" s="8"/>
+      <c r="BV28" s="8"/>
+      <c r="BW28" s="8"/>
+      <c r="BX28" s="8"/>
+      <c r="BY28" s="8"/>
+      <c r="BZ28" s="8"/>
+      <c r="CA28" s="8"/>
+      <c r="CB28" s="8"/>
+      <c r="CC28" s="8"/>
+      <c r="CD28" s="8"/>
+      <c r="CE28" s="8"/>
+      <c r="CF28" s="8"/>
+      <c r="CG28" s="8"/>
+      <c r="CH28" s="8"/>
+      <c r="CI28" s="8"/>
+      <c r="CJ28" s="8"/>
+      <c r="CK28" s="8"/>
+      <c r="CL28" s="8"/>
+      <c r="CM28" s="8"/>
+      <c r="CN28" s="8"/>
+      <c r="CO28" s="8"/>
+      <c r="CP28" s="9"/>
+      <c r="CQ28" s="9"/>
+      <c r="CR28" s="8"/>
+      <c r="CS28" s="8"/>
+      <c r="CT28" s="8"/>
+      <c r="CU28" s="8"/>
+      <c r="CV28" s="8"/>
+      <c r="CW28" s="8"/>
+      <c r="CX28" s="8"/>
+      <c r="CY28" s="8"/>
+      <c r="CZ28" s="8"/>
+      <c r="DA28" s="8"/>
+      <c r="DB28" s="8"/>
+      <c r="DC28" s="8"/>
     </row>
     <row r="29" spans="1:107" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
+      <c r="B29" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>174</v>
+      </c>
       <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="12"/>
+      <c r="H29" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I29" s="11">
+        <v>5841813202</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="N29" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="O29" s="12" t="s">
+        <v>114</v>
+      </c>
       <c r="P29" s="12"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="13"/>
-      <c r="S29" s="14"/>
-      <c r="T29" s="14"/>
-      <c r="U29" s="8"/>
-      <c r="V29" s="8"/>
-      <c r="W29" s="14"/>
-      <c r="X29" s="14"/>
-      <c r="Y29" s="14"/>
-      <c r="Z29" s="14"/>
-      <c r="AA29" s="14"/>
-      <c r="AB29" s="8"/>
-      <c r="AC29" s="8"/>
-      <c r="AD29" s="14"/>
-      <c r="AE29" s="14"/>
-      <c r="AF29" s="14"/>
-      <c r="AG29" s="14"/>
-      <c r="AH29" s="8"/>
-      <c r="AI29" s="8"/>
-      <c r="AJ29" s="8"/>
-      <c r="AK29" s="14"/>
-      <c r="AL29" s="14"/>
-      <c r="AM29" s="14"/>
-      <c r="AN29" s="14"/>
-      <c r="AO29" s="8"/>
-      <c r="AP29" s="8"/>
-      <c r="AQ29" s="8"/>
-      <c r="AR29" s="14"/>
-      <c r="AS29" s="14"/>
-      <c r="AT29" s="14"/>
-      <c r="AU29" s="14"/>
-      <c r="AV29" s="8"/>
-      <c r="AW29" s="8"/>
-      <c r="AX29" s="8"/>
-      <c r="AY29" s="14"/>
-      <c r="AZ29" s="14"/>
-      <c r="BA29" s="14"/>
-      <c r="BB29" s="14"/>
-      <c r="BC29" s="8"/>
-      <c r="BD29" s="8"/>
-      <c r="BE29" s="8"/>
-      <c r="BF29" s="14"/>
-      <c r="BG29" s="14"/>
-      <c r="BH29" s="14"/>
-      <c r="BI29" s="14"/>
-      <c r="BJ29" s="8"/>
-      <c r="BK29" s="8"/>
-      <c r="BL29" s="8"/>
-      <c r="BM29" s="14"/>
-      <c r="BN29" s="14"/>
-      <c r="BO29" s="14"/>
-      <c r="BP29" s="8"/>
-      <c r="BQ29" s="8"/>
-      <c r="BR29" s="14"/>
-      <c r="BS29" s="14"/>
-      <c r="BT29" s="14"/>
-      <c r="BU29" s="8"/>
-      <c r="BV29" s="8"/>
-      <c r="BW29" s="14"/>
-      <c r="BX29" s="14"/>
-      <c r="BY29" s="14"/>
-      <c r="BZ29" s="8"/>
-      <c r="CA29" s="8"/>
-      <c r="CB29" s="14"/>
-      <c r="CC29" s="14"/>
-      <c r="CD29" s="14"/>
-      <c r="CE29" s="8"/>
-      <c r="CF29" s="8"/>
-      <c r="CG29" s="14"/>
-      <c r="CH29" s="14"/>
-      <c r="CI29" s="14"/>
-      <c r="CJ29" s="8"/>
-      <c r="CK29" s="8"/>
-      <c r="CL29" s="14"/>
-      <c r="CM29" s="14"/>
-      <c r="CN29" s="14"/>
-      <c r="CO29" s="14"/>
-      <c r="CP29" s="9"/>
-      <c r="CQ29" s="9"/>
-      <c r="CR29" s="14"/>
-      <c r="CS29" s="14"/>
-      <c r="CT29" s="14"/>
-      <c r="CU29" s="14"/>
-      <c r="CV29" s="8"/>
-      <c r="CW29" s="8"/>
-      <c r="CX29" s="14"/>
-      <c r="CY29" s="14"/>
-      <c r="CZ29" s="14"/>
-      <c r="DA29" s="14"/>
-      <c r="DB29" s="8"/>
-      <c r="DC29" s="8"/>
+      <c r="S29" s="14">
+        <v>0</v>
+      </c>
+      <c r="T29" s="14">
+        <v>0</v>
+      </c>
+      <c r="U29" s="8">
+        <v>0</v>
+      </c>
+      <c r="V29" s="8">
+        <v>0</v>
+      </c>
+      <c r="W29" s="14">
+        <v>0</v>
+      </c>
+      <c r="X29" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="8">
+        <v>2000</v>
+      </c>
+      <c r="AJ29" s="8">
+        <v>2000</v>
+      </c>
+      <c r="AK29" s="14">
+        <v>2</v>
+      </c>
+      <c r="AL29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="8">
+        <v>3000</v>
+      </c>
+      <c r="AQ29" s="8">
+        <v>3000</v>
+      </c>
+      <c r="AR29" s="14">
+        <v>3</v>
+      </c>
+      <c r="AS29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AT29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AU29" s="14">
+        <v>0</v>
+      </c>
+      <c r="AV29" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="AX29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="AY29" s="14">
+        <v>4</v>
+      </c>
+      <c r="AZ29" s="14">
+        <v>0</v>
+      </c>
+      <c r="BA29" s="14">
+        <v>0</v>
+      </c>
+      <c r="BB29" s="14">
+        <v>0</v>
+      </c>
+      <c r="BC29" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="BE29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="BF29" s="14">
+        <v>4</v>
+      </c>
+      <c r="BG29" s="14">
+        <v>0</v>
+      </c>
+      <c r="BH29" s="14">
+        <v>0</v>
+      </c>
+      <c r="BI29" s="14">
+        <v>0</v>
+      </c>
+      <c r="BJ29" s="8">
+        <v>0</v>
+      </c>
+      <c r="BK29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="BL29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="BM29" s="14">
+        <v>4</v>
+      </c>
+      <c r="BN29" s="14">
+        <v>0</v>
+      </c>
+      <c r="BO29" s="14">
+        <v>0</v>
+      </c>
+      <c r="BP29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="BQ29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="BR29" s="14">
+        <v>4</v>
+      </c>
+      <c r="BS29" s="14">
+        <v>0</v>
+      </c>
+      <c r="BT29" s="14">
+        <v>0</v>
+      </c>
+      <c r="BU29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="BV29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="BW29" s="14">
+        <v>4</v>
+      </c>
+      <c r="BX29" s="14">
+        <v>0</v>
+      </c>
+      <c r="BY29" s="14">
+        <v>0</v>
+      </c>
+      <c r="BZ29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="CA29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="CB29" s="14">
+        <v>4</v>
+      </c>
+      <c r="CC29" s="14">
+        <v>0</v>
+      </c>
+      <c r="CD29" s="14">
+        <v>0</v>
+      </c>
+      <c r="CE29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="CF29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="CG29" s="14">
+        <v>4</v>
+      </c>
+      <c r="CH29" s="14">
+        <v>0</v>
+      </c>
+      <c r="CI29" s="14">
+        <v>0</v>
+      </c>
+      <c r="CJ29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="CK29" s="8">
+        <v>4000</v>
+      </c>
+      <c r="CL29" s="14">
+        <v>4</v>
+      </c>
+      <c r="CM29" s="14">
+        <v>0</v>
+      </c>
+      <c r="CN29" s="14">
+        <v>0</v>
+      </c>
+      <c r="CO29" s="14">
+        <v>0</v>
+      </c>
+      <c r="CP29" s="9">
+        <v>37000</v>
+      </c>
+      <c r="CQ29" s="9">
+        <v>37000</v>
+      </c>
+      <c r="CR29" s="14">
+        <v>3.1</v>
+      </c>
+      <c r="CS29" s="14">
+        <v>0</v>
+      </c>
+      <c r="CT29" s="14">
+        <v>0</v>
+      </c>
+      <c r="CU29" s="14">
+        <v>0</v>
+      </c>
+      <c r="CV29" s="8">
+        <v>-37000</v>
+      </c>
+      <c r="CW29" s="8">
+        <v>-37000</v>
+      </c>
+      <c r="CX29" s="14">
+        <v>0</v>
+      </c>
+      <c r="CY29" s="14">
+        <v>0</v>
+      </c>
+      <c r="CZ29" s="14">
+        <v>0</v>
+      </c>
+      <c r="DA29" s="14">
+        <v>0</v>
+      </c>
+      <c r="DB29" s="8">
+        <v>37000</v>
+      </c>
+      <c r="DC29" s="8">
+        <v>37000</v>
+      </c>
     </row>
     <row r="30" spans="1:107" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
@@ -9859,11 +9864,11 @@
         <v>108</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I30" s="5">
         <v>5841813202</v>
@@ -9872,13 +9877,13 @@
         <v>110</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N30" s="5" t="s">
         <v>113</v>
@@ -10172,11 +10177,11 @@
         <v>108</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G31" s="11"/>
       <c r="H31" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I31" s="11">
         <v>5841813202</v>
@@ -10185,13 +10190,13 @@
         <v>110</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N31" s="11" t="s">
         <v>113</v>
@@ -10475,7 +10480,7 @@
       <c r="B32" s="4"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -10492,360 +10497,360 @@
       <c r="Q32" s="7"/>
       <c r="R32" s="7"/>
       <c r="S32" s="8">
-        <f>SUM($S$30:$S$31)</f>
+        <f>SUM($S$29:$S$31)</f>
         <v>0</v>
       </c>
       <c r="T32" s="8">
-        <f>SUM($T$30:$T$31)</f>
+        <f>SUM($T$29:$T$31)</f>
         <v>0</v>
       </c>
       <c r="U32" s="8">
-        <f>SUM($U$30:$U$31)</f>
+        <f>SUM($U$29:$U$31)</f>
         <v>0</v>
       </c>
       <c r="V32" s="8">
-        <f>SUM($V$30:$V$31)</f>
+        <f>SUM($V$29:$V$31)</f>
         <v>0</v>
       </c>
       <c r="W32" s="8">
-        <f>SUM($W$30:$W$31)</f>
+        <f>SUM($W$29:$W$31)</f>
         <v>0</v>
       </c>
       <c r="X32" s="8">
-        <f>SUM($X$30:$X$31)</f>
+        <f>SUM($X$29:$X$31)</f>
         <v>0</v>
       </c>
       <c r="Y32" s="8">
-        <f>SUM($Y$30:$Y$31)</f>
+        <f>SUM($Y$29:$Y$31)</f>
         <v>0</v>
       </c>
       <c r="Z32" s="8">
-        <f>SUM($Z$30:$Z$31)</f>
+        <f>SUM($Z$29:$Z$31)</f>
         <v>0</v>
       </c>
       <c r="AA32" s="8">
-        <f>SUM($AA$30:$AA$31)</f>
+        <f>SUM($AA$29:$AA$31)</f>
         <v>0</v>
       </c>
       <c r="AB32" s="8">
-        <f>SUM($AB$30:$AB$31)</f>
+        <f>SUM($AB$29:$AB$31)</f>
         <v>0</v>
       </c>
       <c r="AC32" s="8">
-        <f>SUM($AC$30:$AC$31)</f>
+        <f>SUM($AC$29:$AC$31)</f>
         <v>0</v>
       </c>
       <c r="AD32" s="8">
-        <f>SUM($AD$30:$AD$31)</f>
+        <f>SUM($AD$29:$AD$31)</f>
         <v>0</v>
       </c>
       <c r="AE32" s="8">
-        <f>SUM($AE$30:$AE$31)</f>
+        <f>SUM($AE$29:$AE$31)</f>
         <v>0</v>
       </c>
       <c r="AF32" s="8">
-        <f>SUM($AF$30:$AF$31)</f>
+        <f>SUM($AF$29:$AF$31)</f>
         <v>0</v>
       </c>
       <c r="AG32" s="8">
-        <f>SUM($AG$30:$AG$31)</f>
+        <f>SUM($AG$29:$AG$31)</f>
         <v>0</v>
       </c>
       <c r="AH32" s="8">
-        <f>SUM($AH$30:$AH$31)</f>
+        <f>SUM($AH$29:$AH$31)</f>
         <v>0</v>
       </c>
       <c r="AI32" s="8">
-        <f>SUM($AI$30:$AI$31)</f>
-        <v>0</v>
+        <f>SUM($AI$29:$AI$31)</f>
+        <v>2000</v>
       </c>
       <c r="AJ32" s="8">
-        <f>SUM($AJ$30:$AJ$31)</f>
-        <v>0</v>
+        <f>SUM($AJ$29:$AJ$31)</f>
+        <v>2000</v>
       </c>
       <c r="AK32" s="8">
-        <f>SUM($AK$30:$AK$31)</f>
-        <v>0</v>
+        <f>SUM($AK$29:$AK$31)</f>
+        <v>2</v>
       </c>
       <c r="AL32" s="8">
-        <f>SUM($AL$30:$AL$31)</f>
+        <f>SUM($AL$29:$AL$31)</f>
         <v>0</v>
       </c>
       <c r="AM32" s="8">
-        <f>SUM($AM$30:$AM$31)</f>
+        <f>SUM($AM$29:$AM$31)</f>
         <v>0</v>
       </c>
       <c r="AN32" s="8">
-        <f>SUM($AN$30:$AN$31)</f>
+        <f>SUM($AN$29:$AN$31)</f>
         <v>0</v>
       </c>
       <c r="AO32" s="8">
-        <f>SUM($AO$30:$AO$31)</f>
+        <f>SUM($AO$29:$AO$31)</f>
         <v>0</v>
       </c>
       <c r="AP32" s="8">
-        <f>SUM($AP$30:$AP$31)</f>
-        <v>0</v>
+        <f>SUM($AP$29:$AP$31)</f>
+        <v>3000</v>
       </c>
       <c r="AQ32" s="8">
-        <f>SUM($AQ$30:$AQ$31)</f>
-        <v>0</v>
+        <f>SUM($AQ$29:$AQ$31)</f>
+        <v>3000</v>
       </c>
       <c r="AR32" s="8">
-        <f>SUM($AR$30:$AR$31)</f>
-        <v>0</v>
+        <f>SUM($AR$29:$AR$31)</f>
+        <v>3</v>
       </c>
       <c r="AS32" s="8">
-        <f>SUM($AS$30:$AS$31)</f>
+        <f>SUM($AS$29:$AS$31)</f>
         <v>0</v>
       </c>
       <c r="AT32" s="8">
-        <f>SUM($AT$30:$AT$31)</f>
+        <f>SUM($AT$29:$AT$31)</f>
         <v>0</v>
       </c>
       <c r="AU32" s="8">
-        <f>SUM($AU$30:$AU$31)</f>
+        <f>SUM($AU$29:$AU$31)</f>
         <v>0</v>
       </c>
       <c r="AV32" s="8">
-        <f>SUM($AV$30:$AV$31)</f>
+        <f>SUM($AV$29:$AV$31)</f>
         <v>0</v>
       </c>
       <c r="AW32" s="8">
-        <f>SUM($AW$30:$AW$31)</f>
-        <v>0</v>
+        <f>SUM($AW$29:$AW$31)</f>
+        <v>4000</v>
       </c>
       <c r="AX32" s="8">
-        <f>SUM($AX$30:$AX$31)</f>
-        <v>0</v>
+        <f>SUM($AX$29:$AX$31)</f>
+        <v>4000</v>
       </c>
       <c r="AY32" s="8">
-        <f>SUM($AY$30:$AY$31)</f>
-        <v>0</v>
+        <f>SUM($AY$29:$AY$31)</f>
+        <v>4</v>
       </c>
       <c r="AZ32" s="8">
-        <f>SUM($AZ$30:$AZ$31)</f>
+        <f>SUM($AZ$29:$AZ$31)</f>
         <v>0</v>
       </c>
       <c r="BA32" s="8">
-        <f>SUM($BA$30:$BA$31)</f>
+        <f>SUM($BA$29:$BA$31)</f>
         <v>0</v>
       </c>
       <c r="BB32" s="8">
-        <f>SUM($BB$30:$BB$31)</f>
+        <f>SUM($BB$29:$BB$31)</f>
         <v>0</v>
       </c>
       <c r="BC32" s="8">
-        <f>SUM($BC$30:$BC$31)</f>
+        <f>SUM($BC$29:$BC$31)</f>
         <v>0</v>
       </c>
       <c r="BD32" s="8">
-        <f>SUM($BD$30:$BD$31)</f>
-        <v>0</v>
+        <f>SUM($BD$29:$BD$31)</f>
+        <v>4000</v>
       </c>
       <c r="BE32" s="8">
-        <f>SUM($BE$30:$BE$31)</f>
-        <v>0</v>
+        <f>SUM($BE$29:$BE$31)</f>
+        <v>4000</v>
       </c>
       <c r="BF32" s="8">
-        <f>SUM($BF$30:$BF$31)</f>
-        <v>0</v>
+        <f>SUM($BF$29:$BF$31)</f>
+        <v>4</v>
       </c>
       <c r="BG32" s="8">
-        <f>SUM($BG$30:$BG$31)</f>
+        <f>SUM($BG$29:$BG$31)</f>
         <v>0</v>
       </c>
       <c r="BH32" s="8">
-        <f>SUM($BH$30:$BH$31)</f>
+        <f>SUM($BH$29:$BH$31)</f>
         <v>0</v>
       </c>
       <c r="BI32" s="8">
-        <f>SUM($BI$30:$BI$31)</f>
+        <f>SUM($BI$29:$BI$31)</f>
         <v>0</v>
       </c>
       <c r="BJ32" s="8">
-        <f>SUM($BJ$30:$BJ$31)</f>
+        <f>SUM($BJ$29:$BJ$31)</f>
         <v>0</v>
       </c>
       <c r="BK32" s="8">
-        <f>SUM($BK$30:$BK$31)</f>
-        <v>0</v>
+        <f>SUM($BK$29:$BK$31)</f>
+        <v>4000</v>
       </c>
       <c r="BL32" s="8">
-        <f>SUM($BL$30:$BL$31)</f>
-        <v>0</v>
+        <f>SUM($BL$29:$BL$31)</f>
+        <v>4000</v>
       </c>
       <c r="BM32" s="8">
-        <f>SUM($BM$30:$BM$31)</f>
-        <v>0</v>
+        <f>SUM($BM$29:$BM$31)</f>
+        <v>4</v>
       </c>
       <c r="BN32" s="8">
-        <f>SUM($BN$30:$BN$31)</f>
+        <f>SUM($BN$29:$BN$31)</f>
         <v>0</v>
       </c>
       <c r="BO32" s="8">
-        <f>SUM($BO$30:$BO$31)</f>
+        <f>SUM($BO$29:$BO$31)</f>
         <v>0</v>
       </c>
       <c r="BP32" s="8">
-        <f>SUM($BP$30:$BP$31)</f>
-        <v>8000</v>
+        <f>SUM($BP$29:$BP$31)</f>
+        <v>12000</v>
       </c>
       <c r="BQ32" s="8">
-        <f>SUM($BQ$30:$BQ$31)</f>
-        <v>8000</v>
+        <f>SUM($BQ$29:$BQ$31)</f>
+        <v>12000</v>
       </c>
       <c r="BR32" s="8">
-        <f>SUM($BR$30:$BR$31)</f>
-        <v>8</v>
+        <f>SUM($BR$29:$BR$31)</f>
+        <v>12</v>
       </c>
       <c r="BS32" s="8">
-        <f>SUM($BS$30:$BS$31)</f>
+        <f>SUM($BS$29:$BS$31)</f>
         <v>0</v>
       </c>
       <c r="BT32" s="8">
-        <f>SUM($BT$30:$BT$31)</f>
+        <f>SUM($BT$29:$BT$31)</f>
         <v>0</v>
       </c>
       <c r="BU32" s="8">
-        <f>SUM($BU$30:$BU$31)</f>
-        <v>8000</v>
+        <f>SUM($BU$29:$BU$31)</f>
+        <v>12000</v>
       </c>
       <c r="BV32" s="8">
-        <f>SUM($BV$30:$BV$31)</f>
-        <v>8000</v>
+        <f>SUM($BV$29:$BV$31)</f>
+        <v>12000</v>
       </c>
       <c r="BW32" s="8">
-        <f>SUM($BW$30:$BW$31)</f>
-        <v>8</v>
+        <f>SUM($BW$29:$BW$31)</f>
+        <v>12</v>
       </c>
       <c r="BX32" s="8">
-        <f>SUM($BX$30:$BX$31)</f>
+        <f>SUM($BX$29:$BX$31)</f>
         <v>0</v>
       </c>
       <c r="BY32" s="8">
-        <f>SUM($BY$30:$BY$31)</f>
+        <f>SUM($BY$29:$BY$31)</f>
         <v>0</v>
       </c>
       <c r="BZ32" s="8">
-        <f>SUM($BZ$30:$BZ$31)</f>
-        <v>8000</v>
+        <f>SUM($BZ$29:$BZ$31)</f>
+        <v>12000</v>
       </c>
       <c r="CA32" s="8">
-        <f>SUM($CA$30:$CA$31)</f>
-        <v>8000</v>
+        <f>SUM($CA$29:$CA$31)</f>
+        <v>12000</v>
       </c>
       <c r="CB32" s="8">
-        <f>SUM($CB$30:$CB$31)</f>
-        <v>8</v>
+        <f>SUM($CB$29:$CB$31)</f>
+        <v>12</v>
       </c>
       <c r="CC32" s="8">
-        <f>SUM($CC$30:$CC$31)</f>
+        <f>SUM($CC$29:$CC$31)</f>
         <v>0</v>
       </c>
       <c r="CD32" s="8">
-        <f>SUM($CD$30:$CD$31)</f>
+        <f>SUM($CD$29:$CD$31)</f>
         <v>0</v>
       </c>
       <c r="CE32" s="8">
-        <f>SUM($CE$30:$CE$31)</f>
-        <v>8000</v>
+        <f>SUM($CE$29:$CE$31)</f>
+        <v>12000</v>
       </c>
       <c r="CF32" s="8">
-        <f>SUM($CF$30:$CF$31)</f>
-        <v>8000</v>
+        <f>SUM($CF$29:$CF$31)</f>
+        <v>12000</v>
       </c>
       <c r="CG32" s="8">
-        <f>SUM($CG$30:$CG$31)</f>
-        <v>8</v>
+        <f>SUM($CG$29:$CG$31)</f>
+        <v>12</v>
       </c>
       <c r="CH32" s="8">
-        <f>SUM($CH$30:$CH$31)</f>
+        <f>SUM($CH$29:$CH$31)</f>
         <v>0</v>
       </c>
       <c r="CI32" s="8">
-        <f>SUM($CI$30:$CI$31)</f>
+        <f>SUM($CI$29:$CI$31)</f>
         <v>0</v>
       </c>
       <c r="CJ32" s="8">
-        <f>SUM($CJ$30:$CJ$31)</f>
-        <v>8000</v>
+        <f>SUM($CJ$29:$CJ$31)</f>
+        <v>12000</v>
       </c>
       <c r="CK32" s="8">
-        <f>SUM($CK$30:$CK$31)</f>
-        <v>8000</v>
+        <f>SUM($CK$29:$CK$31)</f>
+        <v>12000</v>
       </c>
       <c r="CL32" s="8">
-        <f>SUM($CL$30:$CL$31)</f>
-        <v>8</v>
+        <f>SUM($CL$29:$CL$31)</f>
+        <v>12</v>
       </c>
       <c r="CM32" s="8">
-        <f>SUM($CM$30:$CM$31)</f>
+        <f>SUM($CM$29:$CM$31)</f>
         <v>0</v>
       </c>
       <c r="CN32" s="8">
-        <f>SUM($CN$30:$CN$31)</f>
+        <f>SUM($CN$29:$CN$31)</f>
         <v>0</v>
       </c>
       <c r="CO32" s="8">
-        <f>SUM($CO$30:$CO$31)</f>
+        <f>SUM($CO$29:$CO$31)</f>
         <v>0</v>
       </c>
       <c r="CP32" s="9">
-        <f>SUM($CP$30:$CP$31)</f>
-        <v>40000</v>
+        <f>SUM($CP$29:$CP$31)</f>
+        <v>77000</v>
       </c>
       <c r="CQ32" s="9">
-        <f>SUM($CQ$30:$CQ$31)</f>
-        <v>40000</v>
+        <f>SUM($CQ$29:$CQ$31)</f>
+        <v>77000</v>
       </c>
       <c r="CR32" s="8">
-        <f>SUM($CR$30:$CR$31)</f>
-        <v>4</v>
+        <f>SUM($CR$29:$CR$31)</f>
+        <v>7.1</v>
       </c>
       <c r="CS32" s="8">
-        <f>SUM($CS$30:$CS$31)</f>
+        <f>SUM($CS$29:$CS$31)</f>
         <v>0</v>
       </c>
       <c r="CT32" s="8">
-        <f>SUM($CT$30:$CT$31)</f>
+        <f>SUM($CT$29:$CT$31)</f>
         <v>0</v>
       </c>
       <c r="CU32" s="8">
-        <f>SUM($CU$30:$CU$31)</f>
+        <f>SUM($CU$29:$CU$31)</f>
         <v>0</v>
       </c>
       <c r="CV32" s="8">
-        <f>SUM($CV$30:$CV$31)</f>
-        <v>-40000</v>
+        <f>SUM($CV$29:$CV$31)</f>
+        <v>-77000</v>
       </c>
       <c r="CW32" s="8">
-        <f>SUM($CW$30:$CW$31)</f>
-        <v>-40000</v>
+        <f>SUM($CW$29:$CW$31)</f>
+        <v>-77000</v>
       </c>
       <c r="CX32" s="8">
-        <f>SUM($CX$30:$CX$31)</f>
+        <f>SUM($CX$29:$CX$31)</f>
         <v>0</v>
       </c>
       <c r="CY32" s="8">
-        <f>SUM($CY$30:$CY$31)</f>
+        <f>SUM($CY$29:$CY$31)</f>
         <v>0</v>
       </c>
       <c r="CZ32" s="8">
-        <f>SUM($CZ$30:$CZ$31)</f>
+        <f>SUM($CZ$29:$CZ$31)</f>
         <v>0</v>
       </c>
       <c r="DA32" s="8">
-        <f>SUM($DA$30:$DA$31)</f>
+        <f>SUM($DA$29:$DA$31)</f>
         <v>0</v>
       </c>
       <c r="DB32" s="8">
-        <f>SUM($DB$30:$DB$31)</f>
-        <v>40000</v>
+        <f>SUM($DB$29:$DB$31)</f>
+        <v>77000</v>
       </c>
       <c r="DC32" s="8">
-        <f>SUM($DC$30:$DC$31)</f>
-        <v>40000</v>
+        <f>SUM($DC$29:$DC$31)</f>
+        <v>77000</v>
       </c>
     </row>
   </sheetData>

--- a/FMBrandFY2026FebRollingCost20260420.xlsx
+++ b/FMBrandFY2026FebRollingCost20260420.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VBACostCenterSplit\costcentersplit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHENKA~1\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{507D1D23-E7AD-4557-A668-C5598B424A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F0BCD30-6EAE-4D4A-912E-434AFD7412E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{F1622DF8-CD92-4CC1-8765-3E84EA19BB17}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{43669CF1-3978-4373-A0CC-151DEED85F9B}"/>
   </bookViews>
   <sheets>
     <sheet name="CostCenterGroupBySumResult" sheetId="1" r:id="rId1"/>
@@ -578,7 +578,6 @@
   </si>
   <si>
     <t>FM合计：</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1034,8 +1033,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F05DA3B-EA0E-42DC-A440-422B5AF36738}">
-  <dimension ref="A1:DC32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65DBDFD-4B9E-4EF4-8D22-D1A14E81C27D}">
+  <dimension ref="A1:DC33"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:107" x14ac:dyDescent="0.3">
@@ -10853,6 +10852,115 @@
         <v>77000</v>
       </c>
     </row>
+    <row r="33" spans="1:107" x14ac:dyDescent="0.3">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="12"/>
+      <c r="P33" s="12"/>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="13"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="8"/>
+      <c r="V33" s="8"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="14"/>
+      <c r="AA33" s="14"/>
+      <c r="AB33" s="8"/>
+      <c r="AC33" s="8"/>
+      <c r="AD33" s="14"/>
+      <c r="AE33" s="14"/>
+      <c r="AF33" s="14"/>
+      <c r="AG33" s="14"/>
+      <c r="AH33" s="8"/>
+      <c r="AI33" s="8"/>
+      <c r="AJ33" s="8"/>
+      <c r="AK33" s="14"/>
+      <c r="AL33" s="14"/>
+      <c r="AM33" s="14"/>
+      <c r="AN33" s="14"/>
+      <c r="AO33" s="8"/>
+      <c r="AP33" s="8"/>
+      <c r="AQ33" s="8"/>
+      <c r="AR33" s="14"/>
+      <c r="AS33" s="14"/>
+      <c r="AT33" s="14"/>
+      <c r="AU33" s="14"/>
+      <c r="AV33" s="8"/>
+      <c r="AW33" s="8"/>
+      <c r="AX33" s="8"/>
+      <c r="AY33" s="14"/>
+      <c r="AZ33" s="14"/>
+      <c r="BA33" s="14"/>
+      <c r="BB33" s="14"/>
+      <c r="BC33" s="8"/>
+      <c r="BD33" s="8"/>
+      <c r="BE33" s="8"/>
+      <c r="BF33" s="14"/>
+      <c r="BG33" s="14"/>
+      <c r="BH33" s="14"/>
+      <c r="BI33" s="14"/>
+      <c r="BJ33" s="8"/>
+      <c r="BK33" s="8"/>
+      <c r="BL33" s="8"/>
+      <c r="BM33" s="14"/>
+      <c r="BN33" s="14"/>
+      <c r="BO33" s="14"/>
+      <c r="BP33" s="8"/>
+      <c r="BQ33" s="8"/>
+      <c r="BR33" s="14"/>
+      <c r="BS33" s="14"/>
+      <c r="BT33" s="14"/>
+      <c r="BU33" s="8"/>
+      <c r="BV33" s="8"/>
+      <c r="BW33" s="14"/>
+      <c r="BX33" s="14"/>
+      <c r="BY33" s="14"/>
+      <c r="BZ33" s="8"/>
+      <c r="CA33" s="8"/>
+      <c r="CB33" s="14"/>
+      <c r="CC33" s="14"/>
+      <c r="CD33" s="14"/>
+      <c r="CE33" s="8"/>
+      <c r="CF33" s="8"/>
+      <c r="CG33" s="14"/>
+      <c r="CH33" s="14"/>
+      <c r="CI33" s="14"/>
+      <c r="CJ33" s="8"/>
+      <c r="CK33" s="8"/>
+      <c r="CL33" s="14"/>
+      <c r="CM33" s="14"/>
+      <c r="CN33" s="14"/>
+      <c r="CO33" s="14"/>
+      <c r="CP33" s="9"/>
+      <c r="CQ33" s="9"/>
+      <c r="CR33" s="14"/>
+      <c r="CS33" s="14"/>
+      <c r="CT33" s="14"/>
+      <c r="CU33" s="14"/>
+      <c r="CV33" s="8"/>
+      <c r="CW33" s="8"/>
+      <c r="CX33" s="14"/>
+      <c r="CY33" s="14"/>
+      <c r="CZ33" s="14"/>
+      <c r="DA33" s="14"/>
+      <c r="DB33" s="8"/>
+      <c r="DC33" s="8"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/FMBrandFY2026FebRollingCost20260420.xlsx
+++ b/FMBrandFY2026FebRollingCost20260420.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHENKA~1\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F0BCD30-6EAE-4D4A-912E-434AFD7412E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D77B4316-1104-40B6-844A-D0F6755DA340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{43669CF1-3978-4373-A0CC-151DEED85F9B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{6D107D40-96C3-4FDD-8121-D26A6C0D666F}"/>
   </bookViews>
   <sheets>
     <sheet name="CostCenterGroupBySumResult" sheetId="1" r:id="rId1"/>
@@ -533,7 +533,7 @@
     <t>FY26 New Door</t>
   </si>
   <si>
-    <t>合计：</t>
+    <t>Total：</t>
   </si>
   <si>
     <t>KL</t>
@@ -555,7 +555,7 @@
     <t>KLFMFY2026000005</t>
   </si>
   <si>
-    <t>KL合计：</t>
+    <t>KL Total：</t>
   </si>
   <si>
     <t>Y</t>
@@ -577,7 +577,7 @@
     <t>KLFMFY2026000006</t>
   </si>
   <si>
-    <t>FM合计：</t>
+    <t>FM Total：</t>
   </si>
 </sst>
 </file>
@@ -1033,7 +1033,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65DBDFD-4B9E-4EF4-8D22-D1A14E81C27D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A6633D-0ACE-452A-82D8-6836BB785CC9}">
   <dimension ref="A1:DC33"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/FMBrandFY2026FebRollingCost20260420.xlsx
+++ b/FMBrandFY2026FebRollingCost20260420.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHENKA~1\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shenkailing\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D77B4316-1104-40B6-844A-D0F6755DA340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B080F01A-60C3-4BC8-8A94-0DB23C349E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{6D107D40-96C3-4FDD-8121-D26A6C0D666F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17620" xr2:uid="{678EB2BC-7C27-4084-B14A-B7D2584BD678}"/>
   </bookViews>
   <sheets>
     <sheet name="CostCenterGroupBySumResult" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -533,7 +530,7 @@
     <t>FY26 New Door</t>
   </si>
   <si>
-    <t>Total：</t>
+    <t>Total:</t>
   </si>
   <si>
     <t>KL</t>
@@ -555,7 +552,7 @@
     <t>KLFMFY2026000005</t>
   </si>
   <si>
-    <t>KL Total：</t>
+    <t>KL Total:</t>
   </si>
   <si>
     <t>Y</t>
@@ -577,7 +574,7 @@
     <t>KLFMFY2026000006</t>
   </si>
   <si>
-    <t>FM Total：</t>
+    <t>FM Total:</t>
   </si>
 </sst>
 </file>
@@ -1033,7 +1030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A6633D-0ACE-452A-82D8-6836BB785CC9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC48C70B-40F4-47D6-AC64-91DFEEDAD93A}">
   <dimension ref="A1:DC33"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
